--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121314972</v>
+        <v>121313741</v>
       </c>
       <c r="B9" t="n">
-        <v>98071</v>
+        <v>57501</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493938</v>
+        <v>493766</v>
       </c>
       <c r="R9" t="n">
-        <v>6834637</v>
+        <v>6834823</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1465,6 +1465,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,22 +1484,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121313741</v>
+        <v>121314972</v>
       </c>
       <c r="B10" t="n">
-        <v>57501</v>
+        <v>98071</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,13 +1536,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493766</v>
+        <v>493938</v>
       </c>
       <c r="R10" t="n">
-        <v>6834823</v>
+        <v>6834637</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1567,11 +1572,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,12 +1586,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121316297</v>
+        <v>121314407</v>
       </c>
       <c r="B18" t="n">
-        <v>98071</v>
+        <v>79679</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493886</v>
+        <v>493810</v>
       </c>
       <c r="R18" t="n">
-        <v>6834817</v>
+        <v>6834885</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121316463</v>
+        <v>121316297</v>
       </c>
       <c r="B19" t="n">
         <v>98071</v>
@@ -2454,13 +2454,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493838</v>
+        <v>493886</v>
       </c>
       <c r="R19" t="n">
-        <v>6834855</v>
+        <v>6834817</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121314407</v>
+        <v>121316463</v>
       </c>
       <c r="B20" t="n">
-        <v>79679</v>
+        <v>98071</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493810</v>
+        <v>493838</v>
       </c>
       <c r="R20" t="n">
-        <v>6834885</v>
+        <v>6834855</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121314344</v>
+        <v>121314027</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493875</v>
+        <v>493811</v>
       </c>
       <c r="R2" t="n">
-        <v>6834814</v>
+        <v>6834771</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121314211</v>
+        <v>121313915</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493820</v>
+        <v>493790</v>
       </c>
       <c r="R3" t="n">
-        <v>6834777</v>
+        <v>6834789</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121314297</v>
+        <v>121316463</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493861</v>
+        <v>493838</v>
       </c>
       <c r="R4" t="n">
-        <v>6834789</v>
+        <v>6834855</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121314269</v>
+        <v>121314284</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493864</v>
+        <v>493876</v>
       </c>
       <c r="R5" t="n">
-        <v>6834781</v>
+        <v>6834703</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121315050</v>
+        <v>121314199</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493937</v>
+        <v>493816</v>
       </c>
       <c r="R6" t="n">
-        <v>6834639</v>
+        <v>6834773</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121313925</v>
+        <v>121316066</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493790</v>
+        <v>493896</v>
       </c>
       <c r="R7" t="n">
-        <v>6834794</v>
+        <v>6834749</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121316066</v>
+        <v>121316548</v>
       </c>
       <c r="B8" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493896</v>
+        <v>493794</v>
       </c>
       <c r="R8" t="n">
-        <v>6834749</v>
+        <v>6834804</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121313741</v>
+        <v>121314203</v>
       </c>
       <c r="B9" t="n">
-        <v>57501</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493766</v>
+        <v>493870</v>
       </c>
       <c r="R9" t="n">
-        <v>6834823</v>
+        <v>6834767</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1465,11 +1465,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1484,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121314972</v>
+        <v>121315885</v>
       </c>
       <c r="B10" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493938</v>
+        <v>493917</v>
       </c>
       <c r="R10" t="n">
-        <v>6834637</v>
+        <v>6834746</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121316126</v>
+        <v>121315050</v>
       </c>
       <c r="B11" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493898</v>
+        <v>493937</v>
       </c>
       <c r="R11" t="n">
-        <v>6834798</v>
+        <v>6834639</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121316610</v>
+        <v>121316126</v>
       </c>
       <c r="B12" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493818</v>
+        <v>493898</v>
       </c>
       <c r="R12" t="n">
-        <v>6834795</v>
+        <v>6834798</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121314284</v>
+        <v>121313133</v>
       </c>
       <c r="B13" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493876</v>
+        <v>493849</v>
       </c>
       <c r="R13" t="n">
-        <v>6834703</v>
+        <v>6834871</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1880,6 +1875,11 @@
           <t>2024-11-23</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1892,22 +1892,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121313238</v>
+        <v>121313925</v>
       </c>
       <c r="B14" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493815</v>
+        <v>493790</v>
       </c>
       <c r="R14" t="n">
-        <v>6834929</v>
+        <v>6834794</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1994,22 +1994,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121314027</v>
+        <v>121313741</v>
       </c>
       <c r="B15" t="n">
-        <v>78598</v>
+        <v>57504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493811</v>
+        <v>493766</v>
       </c>
       <c r="R15" t="n">
-        <v>6834771</v>
+        <v>6834823</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2082,6 +2082,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,7 +2116,7 @@
         <v>121316679</v>
       </c>
       <c r="B16" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121315452</v>
+        <v>121314344</v>
       </c>
       <c r="B17" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2227,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494000</v>
+        <v>493875</v>
       </c>
       <c r="R17" t="n">
-        <v>6834510</v>
+        <v>6834814</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121314407</v>
+        <v>121313238</v>
       </c>
       <c r="B18" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2357,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493810</v>
+        <v>493815</v>
       </c>
       <c r="R18" t="n">
-        <v>6834885</v>
+        <v>6834929</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121316297</v>
+        <v>121314297</v>
       </c>
       <c r="B19" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493886</v>
+        <v>493861</v>
       </c>
       <c r="R19" t="n">
-        <v>6834817</v>
+        <v>6834789</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121316463</v>
+        <v>121313317</v>
       </c>
       <c r="B20" t="n">
-        <v>98071</v>
+        <v>79711</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2533,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,13 +2561,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493838</v>
+        <v>493813</v>
       </c>
       <c r="R20" t="n">
-        <v>6834855</v>
+        <v>6834953</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2606,22 +2611,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121314199</v>
+        <v>121314407</v>
       </c>
       <c r="B21" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2635,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493816</v>
+        <v>493810</v>
       </c>
       <c r="R21" t="n">
-        <v>6834773</v>
+        <v>6834885</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2708,22 +2713,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121313915</v>
+        <v>121316014</v>
       </c>
       <c r="B22" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2760,13 +2765,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493790</v>
+        <v>493896</v>
       </c>
       <c r="R22" t="n">
-        <v>6834789</v>
+        <v>6834747</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2822,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121316548</v>
+        <v>121314365</v>
       </c>
       <c r="B23" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,13 +2867,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493794</v>
+        <v>493868</v>
       </c>
       <c r="R23" t="n">
-        <v>6834804</v>
+        <v>6834817</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2924,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121313133</v>
+        <v>121316610</v>
       </c>
       <c r="B24" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,25 +2941,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493849</v>
+        <v>493818</v>
       </c>
       <c r="R24" t="n">
-        <v>6834871</v>
+        <v>6834795</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3000,11 +3005,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121315885</v>
+        <v>121314269</v>
       </c>
       <c r="B25" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493917</v>
+        <v>493864</v>
       </c>
       <c r="R25" t="n">
-        <v>6834746</v>
+        <v>6834781</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121314203</v>
+        <v>121315452</v>
       </c>
       <c r="B26" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3145,25 +3145,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493870</v>
+        <v>494000</v>
       </c>
       <c r="R26" t="n">
-        <v>6834767</v>
+        <v>6834510</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121316014</v>
+        <v>121314211</v>
       </c>
       <c r="B27" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493896</v>
+        <v>493820</v>
       </c>
       <c r="R27" t="n">
-        <v>6834747</v>
+        <v>6834777</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3325,22 +3325,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121314365</v>
+        <v>121316297</v>
       </c>
       <c r="B28" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493868</v>
+        <v>493886</v>
       </c>
       <c r="R28" t="n">
         <v>6834817</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121313317</v>
+        <v>121314972</v>
       </c>
       <c r="B29" t="n">
-        <v>79708</v>
+        <v>98081</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3451,25 +3451,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493813</v>
+        <v>493938</v>
       </c>
       <c r="R29" t="n">
-        <v>6834953</v>
+        <v>6834637</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3529,12 +3529,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -2623,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121314407</v>
+        <v>121316014</v>
       </c>
       <c r="B21" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2635,25 +2635,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493810</v>
+        <v>493896</v>
       </c>
       <c r="R21" t="n">
-        <v>6834885</v>
+        <v>6834747</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121316014</v>
+        <v>121314365</v>
       </c>
       <c r="B22" t="n">
         <v>98081</v>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493896</v>
+        <v>493868</v>
       </c>
       <c r="R22" t="n">
-        <v>6834747</v>
+        <v>6834817</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121314365</v>
+        <v>121314407</v>
       </c>
       <c r="B23" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2839,25 +2839,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,13 +2867,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493868</v>
+        <v>493810</v>
       </c>
       <c r="R23" t="n">
-        <v>6834817</v>
+        <v>6834885</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121314344</v>
+        <v>121313238</v>
       </c>
       <c r="B17" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,25 +2227,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493875</v>
+        <v>493815</v>
       </c>
       <c r="R17" t="n">
-        <v>6834814</v>
+        <v>6834929</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121313238</v>
+        <v>121314344</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,25 +2329,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,13 +2357,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493815</v>
+        <v>493875</v>
       </c>
       <c r="R18" t="n">
-        <v>6834929</v>
+        <v>6834814</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121314297</v>
+        <v>121313317</v>
       </c>
       <c r="B19" t="n">
-        <v>98081</v>
+        <v>79711</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,25 +2431,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493861</v>
+        <v>493813</v>
       </c>
       <c r="R19" t="n">
-        <v>6834789</v>
+        <v>6834953</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2509,22 +2509,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121313317</v>
+        <v>121314297</v>
       </c>
       <c r="B20" t="n">
-        <v>79711</v>
+        <v>98081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2533,25 +2533,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,13 +2561,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493813</v>
+        <v>493861</v>
       </c>
       <c r="R20" t="n">
-        <v>6834953</v>
+        <v>6834789</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2611,22 +2611,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121316014</v>
+        <v>121314407</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2635,25 +2635,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493896</v>
+        <v>493810</v>
       </c>
       <c r="R21" t="n">
-        <v>6834747</v>
+        <v>6834885</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121314365</v>
+        <v>121316014</v>
       </c>
       <c r="B22" t="n">
         <v>98081</v>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493868</v>
+        <v>493896</v>
       </c>
       <c r="R22" t="n">
-        <v>6834817</v>
+        <v>6834747</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121314407</v>
+        <v>121314365</v>
       </c>
       <c r="B23" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2839,25 +2839,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,13 +2867,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493810</v>
+        <v>493868</v>
       </c>
       <c r="R23" t="n">
-        <v>6834885</v>
+        <v>6834817</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121314027</v>
+        <v>121316066</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493811</v>
+        <v>493896</v>
       </c>
       <c r="R2" t="n">
-        <v>6834771</v>
+        <v>6834749</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -765,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121313915</v>
+        <v>121316679</v>
       </c>
       <c r="B3" t="n">
         <v>98081</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493790</v>
+        <v>493815</v>
       </c>
       <c r="R3" t="n">
-        <v>6834789</v>
+        <v>6834794</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121316463</v>
+        <v>121315452</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493838</v>
+        <v>494000</v>
       </c>
       <c r="R4" t="n">
-        <v>6834855</v>
+        <v>6834510</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121314284</v>
+        <v>121314199</v>
       </c>
       <c r="B5" t="n">
         <v>98081</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493876</v>
+        <v>493816</v>
       </c>
       <c r="R5" t="n">
-        <v>6834703</v>
+        <v>6834773</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121314199</v>
+        <v>121313133</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493816</v>
+        <v>493849</v>
       </c>
       <c r="R6" t="n">
-        <v>6834773</v>
+        <v>6834871</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1161,6 +1161,11 @@
           <t>2024-11-23</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1173,19 +1178,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121316066</v>
+        <v>121316463</v>
       </c>
       <c r="B7" t="n">
         <v>98081</v>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493896</v>
+        <v>493838</v>
       </c>
       <c r="R7" t="n">
-        <v>6834749</v>
+        <v>6834855</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121316548</v>
+        <v>121314284</v>
       </c>
       <c r="B8" t="n">
         <v>98081</v>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493794</v>
+        <v>493876</v>
       </c>
       <c r="R8" t="n">
-        <v>6834804</v>
+        <v>6834703</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,19 +1382,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121314203</v>
+        <v>121316126</v>
       </c>
       <c r="B9" t="n">
         <v>98081</v>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493870</v>
+        <v>493898</v>
       </c>
       <c r="R9" t="n">
-        <v>6834767</v>
+        <v>6834798</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121315885</v>
+        <v>121316548</v>
       </c>
       <c r="B10" t="n">
         <v>98081</v>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493917</v>
+        <v>493794</v>
       </c>
       <c r="R10" t="n">
-        <v>6834746</v>
+        <v>6834804</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121315050</v>
+        <v>121313317</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>79711</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493937</v>
+        <v>493813</v>
       </c>
       <c r="R11" t="n">
-        <v>6834639</v>
+        <v>6834953</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1683,19 +1688,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121316126</v>
+        <v>121316610</v>
       </c>
       <c r="B12" t="n">
         <v>98081</v>
@@ -1735,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493898</v>
+        <v>493818</v>
       </c>
       <c r="R12" t="n">
-        <v>6834798</v>
+        <v>6834795</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121313133</v>
+        <v>121314297</v>
       </c>
       <c r="B13" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493849</v>
+        <v>493861</v>
       </c>
       <c r="R13" t="n">
-        <v>6834871</v>
+        <v>6834789</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1873,11 +1878,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121313925</v>
+        <v>121314972</v>
       </c>
       <c r="B14" t="n">
         <v>98081</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493790</v>
+        <v>493938</v>
       </c>
       <c r="R14" t="n">
-        <v>6834794</v>
+        <v>6834637</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1994,22 +1994,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121313741</v>
+        <v>121314269</v>
       </c>
       <c r="B15" t="n">
-        <v>57504</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493766</v>
+        <v>493864</v>
       </c>
       <c r="R15" t="n">
-        <v>6834823</v>
+        <v>6834781</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2082,11 +2082,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2101,19 +2096,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121316679</v>
+        <v>121314365</v>
       </c>
       <c r="B16" t="n">
         <v>98081</v>
@@ -2153,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493815</v>
+        <v>493868</v>
       </c>
       <c r="R16" t="n">
-        <v>6834794</v>
+        <v>6834817</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2215,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121313238</v>
+        <v>121314203</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,13 +2250,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493815</v>
+        <v>493870</v>
       </c>
       <c r="R17" t="n">
-        <v>6834929</v>
+        <v>6834767</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2317,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121314344</v>
+        <v>121313925</v>
       </c>
       <c r="B18" t="n">
         <v>98081</v>
@@ -2357,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493875</v>
+        <v>493790</v>
       </c>
       <c r="R18" t="n">
-        <v>6834814</v>
+        <v>6834794</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2407,22 +2402,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121313317</v>
+        <v>121315885</v>
       </c>
       <c r="B19" t="n">
-        <v>79711</v>
+        <v>98081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,13 +2454,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493813</v>
+        <v>493917</v>
       </c>
       <c r="R19" t="n">
-        <v>6834953</v>
+        <v>6834746</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2509,19 +2504,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121314297</v>
+        <v>121313915</v>
       </c>
       <c r="B20" t="n">
         <v>98081</v>
@@ -2561,13 +2556,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493861</v>
+        <v>493790</v>
       </c>
       <c r="R20" t="n">
         <v>6834789</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2623,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121314407</v>
+        <v>121316297</v>
       </c>
       <c r="B21" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2635,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,13 +2658,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493810</v>
+        <v>493886</v>
       </c>
       <c r="R21" t="n">
-        <v>6834885</v>
+        <v>6834817</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2725,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121316014</v>
+        <v>121313238</v>
       </c>
       <c r="B22" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2737,25 +2732,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,13 +2760,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493896</v>
+        <v>493815</v>
       </c>
       <c r="R22" t="n">
-        <v>6834747</v>
+        <v>6834929</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2827,7 +2822,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121314365</v>
+        <v>121314344</v>
       </c>
       <c r="B23" t="n">
         <v>98081</v>
@@ -2867,13 +2862,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493868</v>
+        <v>493875</v>
       </c>
       <c r="R23" t="n">
-        <v>6834817</v>
+        <v>6834814</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2929,7 +2924,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121316610</v>
+        <v>121315050</v>
       </c>
       <c r="B24" t="n">
         <v>98081</v>
@@ -2969,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493818</v>
+        <v>493937</v>
       </c>
       <c r="R24" t="n">
-        <v>6834795</v>
+        <v>6834639</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3031,7 +3026,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121314269</v>
+        <v>121316014</v>
       </c>
       <c r="B25" t="n">
         <v>98081</v>
@@ -3071,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493864</v>
+        <v>493896</v>
       </c>
       <c r="R25" t="n">
-        <v>6834781</v>
+        <v>6834747</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3133,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121315452</v>
+        <v>121314027</v>
       </c>
       <c r="B26" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494000</v>
+        <v>493811</v>
       </c>
       <c r="R26" t="n">
-        <v>6834510</v>
+        <v>6834771</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3223,22 +3218,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121314211</v>
+        <v>121313741</v>
       </c>
       <c r="B27" t="n">
-        <v>98081</v>
+        <v>57504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3247,25 +3242,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493820</v>
+        <v>493766</v>
       </c>
       <c r="R27" t="n">
-        <v>6834777</v>
+        <v>6834823</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3311,6 +3306,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3337,7 +3337,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121316297</v>
+        <v>121314211</v>
       </c>
       <c r="B28" t="n">
         <v>98081</v>
@@ -3377,13 +3377,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493886</v>
+        <v>493820</v>
       </c>
       <c r="R28" t="n">
-        <v>6834817</v>
+        <v>6834777</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3427,22 +3427,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121314972</v>
+        <v>121314407</v>
       </c>
       <c r="B29" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3451,25 +3451,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493938</v>
+        <v>493810</v>
       </c>
       <c r="R29" t="n">
-        <v>6834637</v>
+        <v>6834885</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121313133</v>
+        <v>121316463</v>
       </c>
       <c r="B6" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493849</v>
+        <v>493838</v>
       </c>
       <c r="R6" t="n">
-        <v>6834871</v>
+        <v>6834855</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1159,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121316463</v>
+        <v>121314284</v>
       </c>
       <c r="B7" t="n">
         <v>98081</v>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493838</v>
+        <v>493876</v>
       </c>
       <c r="R7" t="n">
-        <v>6834855</v>
+        <v>6834703</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1280,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121314284</v>
+        <v>121313133</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493876</v>
+        <v>493849</v>
       </c>
       <c r="R8" t="n">
-        <v>6834703</v>
+        <v>6834871</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1370,6 +1365,11 @@
           <t>2024-11-23</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1382,12 +1382,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121313317</v>
+        <v>121316610</v>
       </c>
       <c r="B11" t="n">
-        <v>79711</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493813</v>
+        <v>493818</v>
       </c>
       <c r="R11" t="n">
-        <v>6834953</v>
+        <v>6834795</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1688,19 +1688,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121316610</v>
+        <v>121314297</v>
       </c>
       <c r="B12" t="n">
         <v>98081</v>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493818</v>
+        <v>493861</v>
       </c>
       <c r="R12" t="n">
-        <v>6834795</v>
+        <v>6834789</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121314297</v>
+        <v>121313317</v>
       </c>
       <c r="B13" t="n">
-        <v>98081</v>
+        <v>79711</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493861</v>
+        <v>493813</v>
       </c>
       <c r="R13" t="n">
-        <v>6834789</v>
+        <v>6834953</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,12 +1892,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121313741</v>
+        <v>121314211</v>
       </c>
       <c r="B27" t="n">
-        <v>57504</v>
+        <v>98081</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,25 +3242,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493766</v>
+        <v>493820</v>
       </c>
       <c r="R27" t="n">
-        <v>6834823</v>
+        <v>6834777</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3306,11 +3306,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3337,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121314211</v>
+        <v>121313741</v>
       </c>
       <c r="B28" t="n">
-        <v>98081</v>
+        <v>57504</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3349,25 +3344,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493820</v>
+        <v>493766</v>
       </c>
       <c r="R28" t="n">
-        <v>6834777</v>
+        <v>6834823</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3413,6 +3408,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3539,6 +3539,2619 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121462834</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>494009</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6834570</v>
+      </c>
+      <c r="S30" t="n">
+        <v>9</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121462206</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>493812</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6834571</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121463067</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>493995</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6834619</v>
+      </c>
+      <c r="S32" t="n">
+        <v>9</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gran och tall</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121461113</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78341</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>493790</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6834696</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121463429</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>494075</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6834606</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121460788</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79222</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>493790</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6834696</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121463770</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>494125</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6834588</v>
+      </c>
+      <c r="S36" t="n">
+        <v>9</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Tallstam</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121462959</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98094</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>494001</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6834589</v>
+      </c>
+      <c r="S37" t="n">
+        <v>9</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>121461098</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>493790</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6834696</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121462243</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>493905</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6834568</v>
+      </c>
+      <c r="S39" t="n">
+        <v>9</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121461118</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98094</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>493869</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6834529</v>
+      </c>
+      <c r="S40" t="n">
+        <v>9</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>121461165</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79219</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>493817</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6834627</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121462195</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57504</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>493861</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6834554</v>
+      </c>
+      <c r="S42" t="n">
+        <v>9</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>121461121</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98094</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>493873</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6834530</v>
+      </c>
+      <c r="S43" t="n">
+        <v>9</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>121461485</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79219</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>493825</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6834542</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>121460831</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78340</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Pipmyran, Pipmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>493790</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6834696</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>121464008</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78338</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>494068</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6834592</v>
+      </c>
+      <c r="S46" t="n">
+        <v>12</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>121463160</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78605</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Barkheden, Barkheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>494004</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6834553</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>121461167</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>493883</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6834518</v>
+      </c>
+      <c r="S48" t="n">
+        <v>9</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På Tallstamnen</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>121462937</v>
+      </c>
+      <c r="B49" t="n">
+        <v>74710</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>494004</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6834553</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>121463373</v>
+      </c>
+      <c r="B50" t="n">
+        <v>90674</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>494068</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6834592</v>
+      </c>
+      <c r="S50" t="n">
+        <v>13</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>121462254</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>493917</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6834563</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>121463076</v>
+      </c>
+      <c r="B52" t="n">
+        <v>74708</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>494009</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6834588</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121316066</v>
+        <v>121316297</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493896</v>
+        <v>493886</v>
       </c>
       <c r="R2" t="n">
-        <v>6834749</v>
+        <v>6834817</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121316679</v>
+        <v>121316610</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493815</v>
+        <v>493818</v>
       </c>
       <c r="R3" t="n">
-        <v>6834794</v>
+        <v>6834795</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121315452</v>
+        <v>121316548</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494000</v>
+        <v>493794</v>
       </c>
       <c r="R4" t="n">
-        <v>6834510</v>
+        <v>6834804</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121314199</v>
+        <v>121313133</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493816</v>
+        <v>493849</v>
       </c>
       <c r="R5" t="n">
-        <v>6834773</v>
+        <v>6834871</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,6 +1059,11 @@
           <t>2024-11-23</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1071,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121316463</v>
+        <v>121313317</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>79714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493838</v>
+        <v>493813</v>
       </c>
       <c r="R6" t="n">
-        <v>6834855</v>
+        <v>6834953</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121314284</v>
+        <v>121316014</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493876</v>
+        <v>493896</v>
       </c>
       <c r="R7" t="n">
-        <v>6834703</v>
+        <v>6834747</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1275,22 +1280,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121313133</v>
+        <v>121314027</v>
       </c>
       <c r="B8" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493849</v>
+        <v>493811</v>
       </c>
       <c r="R8" t="n">
-        <v>6834871</v>
+        <v>6834771</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1365,11 +1370,6 @@
           <t>2024-11-23</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På rönn</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1382,22 +1382,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121316126</v>
+        <v>121314344</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493898</v>
+        <v>493875</v>
       </c>
       <c r="R9" t="n">
-        <v>6834798</v>
+        <v>6834814</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121316548</v>
+        <v>121314284</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493794</v>
+        <v>493876</v>
       </c>
       <c r="R10" t="n">
-        <v>6834804</v>
+        <v>6834703</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1586,22 +1586,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121316610</v>
+        <v>121313238</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493818</v>
+        <v>493815</v>
       </c>
       <c r="R11" t="n">
-        <v>6834795</v>
+        <v>6834929</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121314297</v>
+        <v>121315452</v>
       </c>
       <c r="B12" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493861</v>
+        <v>494000</v>
       </c>
       <c r="R12" t="n">
-        <v>6834789</v>
+        <v>6834510</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121313317</v>
+        <v>121316126</v>
       </c>
       <c r="B13" t="n">
-        <v>79711</v>
+        <v>98094</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493813</v>
+        <v>493898</v>
       </c>
       <c r="R13" t="n">
-        <v>6834953</v>
+        <v>6834798</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,12 +1892,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1907,7 +1907,7 @@
         <v>121314972</v>
       </c>
       <c r="B14" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121314269</v>
+        <v>121314211</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493864</v>
+        <v>493820</v>
       </c>
       <c r="R15" t="n">
-        <v>6834781</v>
+        <v>6834777</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2096,22 +2096,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121314365</v>
+        <v>121314297</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493868</v>
+        <v>493861</v>
       </c>
       <c r="R16" t="n">
-        <v>6834817</v>
+        <v>6834789</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121314203</v>
+        <v>121316463</v>
       </c>
       <c r="B17" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493870</v>
+        <v>493838</v>
       </c>
       <c r="R17" t="n">
-        <v>6834767</v>
+        <v>6834855</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121313925</v>
+        <v>121315885</v>
       </c>
       <c r="B18" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493790</v>
+        <v>493917</v>
       </c>
       <c r="R18" t="n">
-        <v>6834794</v>
+        <v>6834746</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2402,22 +2402,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121315885</v>
+        <v>121314199</v>
       </c>
       <c r="B19" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493917</v>
+        <v>493816</v>
       </c>
       <c r="R19" t="n">
-        <v>6834746</v>
+        <v>6834773</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2504,22 +2504,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121313915</v>
+        <v>121314203</v>
       </c>
       <c r="B20" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493790</v>
+        <v>493870</v>
       </c>
       <c r="R20" t="n">
-        <v>6834789</v>
+        <v>6834767</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121316297</v>
+        <v>121314365</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493886</v>
+        <v>493868</v>
       </c>
       <c r="R21" t="n">
         <v>6834817</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121313238</v>
+        <v>121313915</v>
       </c>
       <c r="B22" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,13 +2760,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493815</v>
+        <v>493790</v>
       </c>
       <c r="R22" t="n">
-        <v>6834929</v>
+        <v>6834789</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121314344</v>
+        <v>121314407</v>
       </c>
       <c r="B23" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493875</v>
+        <v>493810</v>
       </c>
       <c r="R23" t="n">
-        <v>6834814</v>
+        <v>6834885</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121315050</v>
+        <v>121313925</v>
       </c>
       <c r="B24" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493937</v>
+        <v>493790</v>
       </c>
       <c r="R24" t="n">
-        <v>6834639</v>
+        <v>6834794</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3014,22 +3014,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121316014</v>
+        <v>121313741</v>
       </c>
       <c r="B25" t="n">
-        <v>98081</v>
+        <v>57504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,13 +3066,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493896</v>
+        <v>493766</v>
       </c>
       <c r="R25" t="n">
-        <v>6834747</v>
+        <v>6834823</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3102,6 +3102,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3116,22 +3121,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121314027</v>
+        <v>121314269</v>
       </c>
       <c r="B26" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,25 +3145,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493811</v>
+        <v>493864</v>
       </c>
       <c r="R26" t="n">
-        <v>6834771</v>
+        <v>6834781</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3218,22 +3223,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121314211</v>
+        <v>121315050</v>
       </c>
       <c r="B27" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3270,13 +3275,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493820</v>
+        <v>493937</v>
       </c>
       <c r="R27" t="n">
-        <v>6834777</v>
+        <v>6834639</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3320,22 +3325,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121313741</v>
+        <v>121316679</v>
       </c>
       <c r="B28" t="n">
-        <v>57504</v>
+        <v>98094</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,25 +3349,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,13 +3377,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493766</v>
+        <v>493815</v>
       </c>
       <c r="R28" t="n">
-        <v>6834823</v>
+        <v>6834794</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3408,11 +3413,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3427,22 +3427,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121314407</v>
+        <v>121316066</v>
       </c>
       <c r="B29" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3451,25 +3451,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493810</v>
+        <v>493896</v>
       </c>
       <c r="R29" t="n">
-        <v>6834885</v>
+        <v>6834749</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121462834</v>
+        <v>121463373</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>90674</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3553,25 +3553,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,13 +3581,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494009</v>
+        <v>494068</v>
       </c>
       <c r="R30" t="n">
-        <v>6834570</v>
+        <v>6834592</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3626,12 +3626,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3646,22 +3641,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121462206</v>
+        <v>121460831</v>
       </c>
       <c r="B31" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3674,37 +3669,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493812</v>
+        <v>493790</v>
       </c>
       <c r="R31" t="n">
-        <v>6834571</v>
+        <v>6834696</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3733,7 +3728,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3743,7 +3738,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3758,19 +3753,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121463067</v>
+        <v>121461098</v>
       </c>
       <c r="B32" t="n">
         <v>78604</v>
@@ -3806,17 +3801,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493995</v>
+        <v>493790</v>
       </c>
       <c r="R32" t="n">
-        <v>6834619</v>
+        <v>6834696</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3845,7 +3840,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3855,12 +3850,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Gran och tall</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3875,22 +3865,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121461113</v>
+        <v>121460832</v>
       </c>
       <c r="B33" t="n">
-        <v>78341</v>
+        <v>79222</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3903,27 +3893,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -3962,7 +3952,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3972,7 +3962,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3999,10 +3989,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121463429</v>
+        <v>121461113</v>
       </c>
       <c r="B34" t="n">
-        <v>78604</v>
+        <v>78341</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4015,37 +4005,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494075</v>
+        <v>493790</v>
       </c>
       <c r="R34" t="n">
-        <v>6834606</v>
+        <v>6834696</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4074,7 +4064,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4084,12 +4074,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4104,22 +4089,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121460788</v>
+        <v>121462254</v>
       </c>
       <c r="B35" t="n">
-        <v>79222</v>
+        <v>98094</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4128,41 +4113,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493790</v>
+        <v>493917</v>
       </c>
       <c r="R35" t="n">
-        <v>6834696</v>
+        <v>6834563</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4189,19 +4174,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>09:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4216,22 +4191,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121463770</v>
+        <v>121462937</v>
       </c>
       <c r="B36" t="n">
-        <v>78604</v>
+        <v>74710</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4244,37 +4219,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494125</v>
+        <v>494004</v>
       </c>
       <c r="R36" t="n">
-        <v>6834588</v>
+        <v>6834553</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4303,7 +4278,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4313,12 +4288,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Tallstam</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4333,22 +4303,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121462959</v>
+        <v>121462206</v>
       </c>
       <c r="B37" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4357,50 +4327,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494001</v>
+        <v>493812</v>
       </c>
       <c r="R37" t="n">
-        <v>6834589</v>
+        <v>6834571</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4429,7 +4390,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4439,7 +4400,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4454,22 +4415,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121461098</v>
+        <v>121463160</v>
       </c>
       <c r="B38" t="n">
-        <v>78601</v>
+        <v>78605</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4482,16 +4443,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4500,16 +4461,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Barkheden, Barkheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493790</v>
+        <v>494004</v>
       </c>
       <c r="R38" t="n">
-        <v>6834696</v>
+        <v>6834553</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4541,7 +4505,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4551,7 +4515,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4560,6 +4524,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4571,17 +4536,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121462243</v>
+        <v>121461485</v>
       </c>
       <c r="B39" t="n">
-        <v>78601</v>
+        <v>79222</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4594,37 +4559,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493905</v>
+        <v>493825</v>
       </c>
       <c r="R39" t="n">
-        <v>6834568</v>
+        <v>6834542</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4653,7 +4618,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4663,7 +4628,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4678,22 +4643,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121461118</v>
+        <v>121463076</v>
       </c>
       <c r="B40" t="n">
-        <v>98094</v>
+        <v>74710</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4702,50 +4667,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493869</v>
+        <v>494009</v>
       </c>
       <c r="R40" t="n">
-        <v>6834529</v>
+        <v>6834588</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4774,7 +4730,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4784,7 +4740,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4799,22 +4755,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121461165</v>
+        <v>121461117</v>
       </c>
       <c r="B41" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4886,7 +4842,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4852,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,10 +4879,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121462195</v>
+        <v>121464008</v>
       </c>
       <c r="B42" t="n">
-        <v>57504</v>
+        <v>78341</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4939,37 +4895,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493861</v>
+        <v>494068</v>
       </c>
       <c r="R42" t="n">
-        <v>6834554</v>
+        <v>6834592</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4998,7 +4954,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5008,7 +4964,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5023,19 +4979,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121461121</v>
+        <v>121463365</v>
       </c>
       <c r="B43" t="n">
         <v>98094</v>
@@ -5068,20 +5024,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493873</v>
+        <v>494086</v>
       </c>
       <c r="R43" t="n">
-        <v>6834530</v>
+        <v>6834603</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5110,7 +5078,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5120,7 +5088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5129,28 +5097,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121461485</v>
+        <v>121463743</v>
       </c>
       <c r="B44" t="n">
-        <v>79219</v>
+        <v>98094</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5159,41 +5128,53 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493825</v>
+        <v>494116</v>
       </c>
       <c r="R44" t="n">
-        <v>6834542</v>
+        <v>6834573</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5222,7 +5203,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5232,7 +5213,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5241,28 +5222,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121460831</v>
+        <v>121463131</v>
       </c>
       <c r="B45" t="n">
-        <v>78340</v>
+        <v>98094</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5271,41 +5253,53 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493790</v>
+        <v>494081</v>
       </c>
       <c r="R45" t="n">
-        <v>6834696</v>
+        <v>6834614</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5334,7 +5328,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5344,7 +5338,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5353,28 +5347,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121464008</v>
+        <v>121461118</v>
       </c>
       <c r="B46" t="n">
-        <v>78338</v>
+        <v>98095</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5383,41 +5378,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494068</v>
+        <v>493869</v>
       </c>
       <c r="R46" t="n">
-        <v>6834592</v>
+        <v>6834529</v>
       </c>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5446,7 +5450,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5456,7 +5460,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5471,22 +5475,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121463160</v>
+        <v>121462243</v>
       </c>
       <c r="B47" t="n">
-        <v>78605</v>
+        <v>78604</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5499,16 +5503,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5517,22 +5521,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Barkheden, Barkheden, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494004</v>
+        <v>493905</v>
       </c>
       <c r="R47" t="n">
-        <v>6834553</v>
+        <v>6834568</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5561,7 +5562,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5571,7 +5572,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5580,29 +5581,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121461167</v>
+        <v>121461121</v>
       </c>
       <c r="B48" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5611,38 +5611,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493883</v>
+        <v>493873</v>
       </c>
       <c r="R48" t="n">
-        <v>6834518</v>
+        <v>6834530</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5687,11 +5687,6 @@
           <t>09:58</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På Tallstamnen</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5709,17 +5704,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121462937</v>
+        <v>121461167</v>
       </c>
       <c r="B49" t="n">
-        <v>74710</v>
+        <v>78604</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5732,37 +5727,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494004</v>
+        <v>493883</v>
       </c>
       <c r="R49" t="n">
-        <v>6834553</v>
+        <v>6834518</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5791,7 +5786,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5801,7 +5796,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På Tallstamnen</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5816,22 +5816,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121463373</v>
+        <v>121463067</v>
       </c>
       <c r="B50" t="n">
-        <v>90674</v>
+        <v>78604</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5840,25 +5840,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5868,13 +5868,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494068</v>
+        <v>493995</v>
       </c>
       <c r="R50" t="n">
-        <v>6834592</v>
+        <v>6834619</v>
       </c>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5913,7 +5913,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Gran och tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5928,22 +5933,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121462254</v>
+        <v>121463429</v>
       </c>
       <c r="B51" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5952,41 +5957,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493917</v>
+        <v>494075</v>
       </c>
       <c r="R51" t="n">
-        <v>6834563</v>
+        <v>6834606</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6013,9 +6018,24 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6030,22 +6050,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121463076</v>
+        <v>121462195</v>
       </c>
       <c r="B52" t="n">
-        <v>74708</v>
+        <v>57504</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6058,37 +6078,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494009</v>
+        <v>493861</v>
       </c>
       <c r="R52" t="n">
-        <v>6834588</v>
+        <v>6834554</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6117,7 +6137,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6127,7 +6147,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6142,15 +6162,370 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>121463770</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>494125</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6834588</v>
+      </c>
+      <c r="S53" t="n">
+        <v>9</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Tallstam</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>121462959</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98095</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>494001</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6834589</v>
+      </c>
+      <c r="S54" t="n">
+        <v>9</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>121462834</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>494009</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6834570</v>
+      </c>
+      <c r="S55" t="n">
+        <v>9</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121316297</v>
+        <v>121313317</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>79714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493886</v>
+        <v>493813</v>
       </c>
       <c r="R2" t="n">
-        <v>6834817</v>
+        <v>6834953</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121316610</v>
+        <v>121314284</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493818</v>
+        <v>493876</v>
       </c>
       <c r="R3" t="n">
-        <v>6834795</v>
+        <v>6834703</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121316548</v>
+        <v>121315050</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493794</v>
+        <v>493937</v>
       </c>
       <c r="R4" t="n">
-        <v>6834804</v>
+        <v>6834639</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121313133</v>
+        <v>121316679</v>
       </c>
       <c r="B5" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493849</v>
+        <v>493815</v>
       </c>
       <c r="R5" t="n">
-        <v>6834871</v>
+        <v>6834794</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121313317</v>
+        <v>121314269</v>
       </c>
       <c r="B6" t="n">
-        <v>79714</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493813</v>
+        <v>493864</v>
       </c>
       <c r="R6" t="n">
-        <v>6834953</v>
+        <v>6834781</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121316014</v>
+        <v>121315885</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493896</v>
+        <v>493917</v>
       </c>
       <c r="R7" t="n">
-        <v>6834747</v>
+        <v>6834746</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121314027</v>
+        <v>121314365</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493811</v>
+        <v>493868</v>
       </c>
       <c r="R8" t="n">
-        <v>6834771</v>
+        <v>6834817</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,12 +1377,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1397,7 +1392,7 @@
         <v>121314344</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121314284</v>
+        <v>121314297</v>
       </c>
       <c r="B10" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493876</v>
+        <v>493861</v>
       </c>
       <c r="R10" t="n">
-        <v>6834703</v>
+        <v>6834789</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1586,22 +1581,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121313238</v>
+        <v>121314972</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493815</v>
+        <v>493938</v>
       </c>
       <c r="R11" t="n">
-        <v>6834929</v>
+        <v>6834637</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121315452</v>
+        <v>121313925</v>
       </c>
       <c r="B12" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494000</v>
+        <v>493790</v>
       </c>
       <c r="R12" t="n">
-        <v>6834510</v>
+        <v>6834794</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1790,22 +1785,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121316126</v>
+        <v>121313915</v>
       </c>
       <c r="B13" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493898</v>
+        <v>493790</v>
       </c>
       <c r="R13" t="n">
-        <v>6834798</v>
+        <v>6834789</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121314972</v>
+        <v>121314199</v>
       </c>
       <c r="B14" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493938</v>
+        <v>493816</v>
       </c>
       <c r="R14" t="n">
-        <v>6834637</v>
+        <v>6834773</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1994,22 +1989,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121314211</v>
+        <v>121316126</v>
       </c>
       <c r="B15" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,13 +2041,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493820</v>
+        <v>493898</v>
       </c>
       <c r="R15" t="n">
-        <v>6834777</v>
+        <v>6834798</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2096,22 +2091,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121314297</v>
+        <v>121316066</v>
       </c>
       <c r="B16" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,13 +2143,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493861</v>
+        <v>493896</v>
       </c>
       <c r="R16" t="n">
-        <v>6834789</v>
+        <v>6834749</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121316463</v>
+        <v>121314203</v>
       </c>
       <c r="B17" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493838</v>
+        <v>493870</v>
       </c>
       <c r="R17" t="n">
-        <v>6834855</v>
+        <v>6834767</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121315885</v>
+        <v>121313741</v>
       </c>
       <c r="B18" t="n">
-        <v>98094</v>
+        <v>57504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2347,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493917</v>
+        <v>493766</v>
       </c>
       <c r="R18" t="n">
-        <v>6834746</v>
+        <v>6834823</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2388,6 +2383,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,22 +2402,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121314199</v>
+        <v>121315452</v>
       </c>
       <c r="B19" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493816</v>
+        <v>494000</v>
       </c>
       <c r="R19" t="n">
-        <v>6834773</v>
+        <v>6834510</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2504,22 +2504,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121314203</v>
+        <v>121316014</v>
       </c>
       <c r="B20" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493870</v>
+        <v>493896</v>
       </c>
       <c r="R20" t="n">
-        <v>6834767</v>
+        <v>6834747</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121314365</v>
+        <v>121314407</v>
       </c>
       <c r="B21" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493868</v>
+        <v>493810</v>
       </c>
       <c r="R21" t="n">
-        <v>6834817</v>
+        <v>6834885</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121313915</v>
+        <v>121314027</v>
       </c>
       <c r="B22" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,13 +2760,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493790</v>
+        <v>493811</v>
       </c>
       <c r="R22" t="n">
-        <v>6834789</v>
+        <v>6834771</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2810,19 +2810,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121314407</v>
+        <v>121313133</v>
       </c>
       <c r="B23" t="n">
         <v>79685</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493810</v>
+        <v>493849</v>
       </c>
       <c r="R23" t="n">
-        <v>6834885</v>
+        <v>6834871</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2898,6 +2898,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2924,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121313925</v>
+        <v>121314211</v>
       </c>
       <c r="B24" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2964,13 +2969,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493790</v>
+        <v>493820</v>
       </c>
       <c r="R24" t="n">
-        <v>6834794</v>
+        <v>6834777</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3026,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121313741</v>
+        <v>121316463</v>
       </c>
       <c r="B25" t="n">
-        <v>57504</v>
+        <v>98095</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3043,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,13 +3071,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493766</v>
+        <v>493838</v>
       </c>
       <c r="R25" t="n">
-        <v>6834823</v>
+        <v>6834855</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3102,11 +3107,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3121,22 +3121,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121314269</v>
+        <v>121313238</v>
       </c>
       <c r="B26" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3145,25 +3145,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493864</v>
+        <v>493815</v>
       </c>
       <c r="R26" t="n">
-        <v>6834781</v>
+        <v>6834929</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121315050</v>
+        <v>121316610</v>
       </c>
       <c r="B27" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493937</v>
+        <v>493818</v>
       </c>
       <c r="R27" t="n">
-        <v>6834639</v>
+        <v>6834795</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121316679</v>
+        <v>121316297</v>
       </c>
       <c r="B28" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3377,13 +3377,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493815</v>
+        <v>493886</v>
       </c>
       <c r="R28" t="n">
-        <v>6834794</v>
+        <v>6834817</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121316066</v>
+        <v>121316548</v>
       </c>
       <c r="B29" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493896</v>
+        <v>493794</v>
       </c>
       <c r="R29" t="n">
-        <v>6834749</v>
+        <v>6834804</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121463373</v>
+        <v>121461165</v>
       </c>
       <c r="B30" t="n">
-        <v>90674</v>
+        <v>79222</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3553,41 +3553,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494068</v>
+        <v>493817</v>
       </c>
       <c r="R30" t="n">
-        <v>6834592</v>
+        <v>6834627</v>
       </c>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3641,22 +3641,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121460831</v>
+        <v>121462937</v>
       </c>
       <c r="B31" t="n">
-        <v>78340</v>
+        <v>74710</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3669,34 +3669,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493790</v>
+        <v>494004</v>
       </c>
       <c r="R31" t="n">
-        <v>6834696</v>
+        <v>6834553</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3765,10 +3765,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121461098</v>
+        <v>121462254</v>
       </c>
       <c r="B32" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3777,41 +3777,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493790</v>
+        <v>493917</v>
       </c>
       <c r="R32" t="n">
-        <v>6834696</v>
+        <v>6834563</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3838,19 +3838,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>09:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,22 +3855,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121460832</v>
+        <v>121464008</v>
       </c>
       <c r="B33" t="n">
-        <v>79222</v>
+        <v>78341</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3893,37 +3883,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493790</v>
+        <v>494068</v>
       </c>
       <c r="R33" t="n">
-        <v>6834696</v>
+        <v>6834592</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3952,7 +3942,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3962,7 +3952,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3977,22 +3967,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121461113</v>
+        <v>121461098</v>
       </c>
       <c r="B34" t="n">
-        <v>78341</v>
+        <v>78604</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4005,21 +3995,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4064,7 +4054,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4074,7 +4064,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4094,17 +4084,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121462254</v>
+        <v>121463373</v>
       </c>
       <c r="B35" t="n">
-        <v>98094</v>
+        <v>90675</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4113,41 +4103,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493917</v>
+        <v>494068</v>
       </c>
       <c r="R35" t="n">
-        <v>6834563</v>
+        <v>6834592</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4174,9 +4164,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4191,22 +4191,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121462937</v>
+        <v>121463160</v>
       </c>
       <c r="B36" t="n">
-        <v>74710</v>
+        <v>78605</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4219,27 +4219,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>230405</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Barkheden, Barkheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -4278,7 +4281,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4288,7 +4291,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4297,6 +4300,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4427,10 +4431,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121463160</v>
+        <v>121463076</v>
       </c>
       <c r="B38" t="n">
-        <v>78605</v>
+        <v>74710</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4443,40 +4447,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>230405</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barkheden, Barkheden, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494004</v>
+        <v>494009</v>
       </c>
       <c r="R38" t="n">
-        <v>6834553</v>
+        <v>6834588</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4505,7 +4506,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4515,7 +4516,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4524,26 +4525,25 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121461485</v>
+        <v>121460788</v>
       </c>
       <c r="B39" t="n">
         <v>79222</v>
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493825</v>
+        <v>493790</v>
       </c>
       <c r="R39" t="n">
-        <v>6834542</v>
+        <v>6834696</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4648,17 +4648,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121463076</v>
+        <v>121461485</v>
       </c>
       <c r="B40" t="n">
-        <v>74710</v>
+        <v>79222</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4671,37 +4671,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494009</v>
+        <v>493825</v>
       </c>
       <c r="R40" t="n">
-        <v>6834588</v>
+        <v>6834542</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4755,22 +4755,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121461117</v>
+        <v>121460831</v>
       </c>
       <c r="B41" t="n">
-        <v>79222</v>
+        <v>78340</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4783,34 +4783,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493817</v>
+        <v>493790</v>
       </c>
       <c r="R41" t="n">
-        <v>6834627</v>
+        <v>6834696</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4872,14 +4872,14 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121464008</v>
+        <v>121461113</v>
       </c>
       <c r="B42" t="n">
         <v>78341</v>
@@ -4915,17 +4915,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494068</v>
+        <v>493790</v>
       </c>
       <c r="R42" t="n">
-        <v>6834592</v>
+        <v>6834696</v>
       </c>
       <c r="S42" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4979,22 +4979,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121463365</v>
+        <v>121463131</v>
       </c>
       <c r="B43" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494086</v>
+        <v>494081</v>
       </c>
       <c r="R43" t="n">
-        <v>6834603</v>
+        <v>6834614</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5119,7 +5119,7 @@
         <v>121463743</v>
       </c>
       <c r="B44" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121463131</v>
+        <v>121463365</v>
       </c>
       <c r="B45" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494081</v>
+        <v>494086</v>
       </c>
       <c r="R45" t="n">
-        <v>6834614</v>
+        <v>6834603</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5366,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121461118</v>
+        <v>121462195</v>
       </c>
       <c r="B46" t="n">
-        <v>98095</v>
+        <v>57504</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5378,47 +5378,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493869</v>
+        <v>493861</v>
       </c>
       <c r="R46" t="n">
-        <v>6834529</v>
+        <v>6834554</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5450,7 +5441,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5460,7 +5451,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5487,7 +5478,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121462243</v>
+        <v>121463429</v>
       </c>
       <c r="B47" t="n">
         <v>78604</v>
@@ -5527,10 +5518,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493905</v>
+        <v>494075</v>
       </c>
       <c r="R47" t="n">
-        <v>6834568</v>
+        <v>6834606</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5562,7 +5553,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5572,7 +5563,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5599,10 +5595,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121461121</v>
+        <v>121462834</v>
       </c>
       <c r="B48" t="n">
-        <v>98095</v>
+        <v>78604</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5611,38 +5607,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493873</v>
+        <v>494009</v>
       </c>
       <c r="R48" t="n">
-        <v>6834530</v>
+        <v>6834570</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5674,7 +5670,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5684,7 +5680,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5711,7 +5712,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121461167</v>
+        <v>121462243</v>
       </c>
       <c r="B49" t="n">
         <v>78604</v>
@@ -5751,10 +5752,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493883</v>
+        <v>493905</v>
       </c>
       <c r="R49" t="n">
-        <v>6834518</v>
+        <v>6834568</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -5786,7 +5787,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5796,12 +5797,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På Tallstamnen</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5828,7 +5824,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121463067</v>
+        <v>121461167</v>
       </c>
       <c r="B50" t="n">
         <v>78604</v>
@@ -5868,10 +5864,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493995</v>
+        <v>493883</v>
       </c>
       <c r="R50" t="n">
-        <v>6834619</v>
+        <v>6834518</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -5903,7 +5899,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5913,12 +5909,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Gran och tall</t>
+          <t>På Tallstamnen</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5945,7 +5941,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121463429</v>
+        <v>121463770</v>
       </c>
       <c r="B51" t="n">
         <v>78604</v>
@@ -5985,10 +5981,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494075</v>
+        <v>494125</v>
       </c>
       <c r="R51" t="n">
-        <v>6834606</v>
+        <v>6834588</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6020,7 +6016,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6030,12 +6026,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Tallstam</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6062,10 +6058,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121462195</v>
+        <v>121461118</v>
       </c>
       <c r="B52" t="n">
-        <v>57504</v>
+        <v>98095</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6074,38 +6070,47 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493861</v>
+        <v>493869</v>
       </c>
       <c r="R52" t="n">
-        <v>6834554</v>
+        <v>6834529</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6137,7 +6142,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6147,7 +6152,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6174,7 +6179,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121463770</v>
+        <v>121463067</v>
       </c>
       <c r="B53" t="n">
         <v>78604</v>
@@ -6214,10 +6219,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494125</v>
+        <v>493995</v>
       </c>
       <c r="R53" t="n">
-        <v>6834588</v>
+        <v>6834619</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6249,7 +6254,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6259,12 +6264,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Tallstam</t>
+          <t>Gran och tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6291,7 +6296,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121462959</v>
+        <v>121461121</v>
       </c>
       <c r="B54" t="n">
         <v>98095</v>
@@ -6324,26 +6329,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494001</v>
+        <v>493873</v>
       </c>
       <c r="R54" t="n">
-        <v>6834589</v>
+        <v>6834530</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6375,7 +6371,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6385,7 +6381,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6412,10 +6408,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121462834</v>
+        <v>121462959</v>
       </c>
       <c r="B55" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6424,38 +6420,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494009</v>
+        <v>494001</v>
       </c>
       <c r="R55" t="n">
-        <v>6834570</v>
+        <v>6834589</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6487,7 +6492,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6497,12 +6502,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121313317</v>
+        <v>121316463</v>
       </c>
       <c r="B2" t="n">
-        <v>79714</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493813</v>
+        <v>493838</v>
       </c>
       <c r="R2" t="n">
-        <v>6834953</v>
+        <v>6834855</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121314284</v>
+        <v>121314972</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493876</v>
+        <v>493938</v>
       </c>
       <c r="R3" t="n">
-        <v>6834703</v>
+        <v>6834637</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121315050</v>
+        <v>121314297</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493937</v>
+        <v>493861</v>
       </c>
       <c r="R4" t="n">
-        <v>6834639</v>
+        <v>6834789</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121316679</v>
+        <v>121316014</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493815</v>
+        <v>493896</v>
       </c>
       <c r="R5" t="n">
-        <v>6834794</v>
+        <v>6834747</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121314269</v>
+        <v>121314203</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493864</v>
+        <v>493870</v>
       </c>
       <c r="R6" t="n">
-        <v>6834781</v>
+        <v>6834767</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121315885</v>
+        <v>121313238</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493917</v>
+        <v>493815</v>
       </c>
       <c r="R7" t="n">
-        <v>6834746</v>
+        <v>6834929</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121314365</v>
+        <v>121314284</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493868</v>
+        <v>493876</v>
       </c>
       <c r="R8" t="n">
-        <v>6834817</v>
+        <v>6834703</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121314344</v>
+        <v>121313925</v>
       </c>
       <c r="B9" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493875</v>
+        <v>493790</v>
       </c>
       <c r="R9" t="n">
-        <v>6834814</v>
+        <v>6834794</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1479,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121314297</v>
+        <v>121316126</v>
       </c>
       <c r="B10" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493861</v>
+        <v>493898</v>
       </c>
       <c r="R10" t="n">
-        <v>6834789</v>
+        <v>6834798</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121314972</v>
+        <v>121316548</v>
       </c>
       <c r="B11" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493938</v>
+        <v>493794</v>
       </c>
       <c r="R11" t="n">
-        <v>6834637</v>
+        <v>6834804</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121313925</v>
+        <v>121314027</v>
       </c>
       <c r="B12" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493790</v>
+        <v>493811</v>
       </c>
       <c r="R12" t="n">
-        <v>6834794</v>
+        <v>6834771</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1800,7 +1800,7 @@
         <v>121313915</v>
       </c>
       <c r="B13" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>121314199</v>
       </c>
       <c r="B14" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121316126</v>
+        <v>121315885</v>
       </c>
       <c r="B15" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493898</v>
+        <v>493917</v>
       </c>
       <c r="R15" t="n">
-        <v>6834798</v>
+        <v>6834746</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121316066</v>
+        <v>121313317</v>
       </c>
       <c r="B16" t="n">
-        <v>98095</v>
+        <v>79717</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493896</v>
+        <v>493813</v>
       </c>
       <c r="R16" t="n">
-        <v>6834749</v>
+        <v>6834953</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2193,22 +2193,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121314203</v>
+        <v>121314365</v>
       </c>
       <c r="B17" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,13 +2245,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493870</v>
+        <v>493868</v>
       </c>
       <c r="R17" t="n">
-        <v>6834767</v>
+        <v>6834817</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121313741</v>
+        <v>121315050</v>
       </c>
       <c r="B18" t="n">
-        <v>57504</v>
+        <v>98098</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493766</v>
+        <v>493937</v>
       </c>
       <c r="R18" t="n">
-        <v>6834823</v>
+        <v>6834639</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2383,11 +2383,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,22 +2397,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121315452</v>
+        <v>121314344</v>
       </c>
       <c r="B19" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494000</v>
+        <v>493875</v>
       </c>
       <c r="R19" t="n">
-        <v>6834510</v>
+        <v>6834814</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2516,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121316014</v>
+        <v>121316066</v>
       </c>
       <c r="B20" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2559,7 +2554,7 @@
         <v>493896</v>
       </c>
       <c r="R20" t="n">
-        <v>6834747</v>
+        <v>6834749</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2618,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121314407</v>
+        <v>121314211</v>
       </c>
       <c r="B21" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,13 +2653,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493810</v>
+        <v>493820</v>
       </c>
       <c r="R21" t="n">
-        <v>6834885</v>
+        <v>6834777</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2708,22 +2703,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121314027</v>
+        <v>121314269</v>
       </c>
       <c r="B22" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2727,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493811</v>
+        <v>493864</v>
       </c>
       <c r="R22" t="n">
-        <v>6834771</v>
+        <v>6834781</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2810,22 +2805,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121313133</v>
+        <v>121316297</v>
       </c>
       <c r="B23" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,25 +2829,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,13 +2857,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493849</v>
+        <v>493886</v>
       </c>
       <c r="R23" t="n">
-        <v>6834871</v>
+        <v>6834817</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2898,11 +2893,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2929,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121314211</v>
+        <v>121316610</v>
       </c>
       <c r="B24" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2969,13 +2959,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493820</v>
+        <v>493818</v>
       </c>
       <c r="R24" t="n">
-        <v>6834777</v>
+        <v>6834795</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3019,22 +3009,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121316463</v>
+        <v>121315452</v>
       </c>
       <c r="B25" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3043,25 +3033,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493838</v>
+        <v>494000</v>
       </c>
       <c r="R25" t="n">
-        <v>6834855</v>
+        <v>6834510</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3133,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121313238</v>
+        <v>121313741</v>
       </c>
       <c r="B26" t="n">
-        <v>78604</v>
+        <v>57507</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,13 +3163,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493815</v>
+        <v>493766</v>
       </c>
       <c r="R26" t="n">
-        <v>6834929</v>
+        <v>6834823</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3209,6 +3199,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3223,22 +3218,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121316610</v>
+        <v>121314407</v>
       </c>
       <c r="B27" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3247,25 +3242,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493818</v>
+        <v>493810</v>
       </c>
       <c r="R27" t="n">
-        <v>6834795</v>
+        <v>6834885</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3337,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121316297</v>
+        <v>121313133</v>
       </c>
       <c r="B28" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3349,25 +3344,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,13 +3372,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493886</v>
+        <v>493849</v>
       </c>
       <c r="R28" t="n">
-        <v>6834817</v>
+        <v>6834871</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3413,6 +3408,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121316548</v>
+        <v>121316679</v>
       </c>
       <c r="B29" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493794</v>
+        <v>493815</v>
       </c>
       <c r="R29" t="n">
-        <v>6834804</v>
+        <v>6834794</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121461165</v>
+        <v>121463160</v>
       </c>
       <c r="B30" t="n">
-        <v>79222</v>
+        <v>78608</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,34 +3557,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>230405</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Barkheden, Barkheden, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493817</v>
+        <v>494004</v>
       </c>
       <c r="R30" t="n">
-        <v>6834627</v>
+        <v>6834553</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3616,7 +3619,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3626,7 +3629,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3635,6 +3638,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3646,17 +3650,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121462937</v>
+        <v>121461098</v>
       </c>
       <c r="B31" t="n">
-        <v>74710</v>
+        <v>78607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3669,21 +3673,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3693,10 +3697,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494004</v>
+        <v>493790</v>
       </c>
       <c r="R31" t="n">
-        <v>6834553</v>
+        <v>6834696</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3728,7 +3732,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3738,7 +3742,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3758,17 +3762,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121462254</v>
+        <v>121461113</v>
       </c>
       <c r="B32" t="n">
-        <v>98095</v>
+        <v>78344</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3777,41 +3781,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493917</v>
+        <v>493790</v>
       </c>
       <c r="R32" t="n">
-        <v>6834563</v>
+        <v>6834696</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3838,9 +3842,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3855,22 +3869,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121464008</v>
+        <v>121460831</v>
       </c>
       <c r="B33" t="n">
-        <v>78341</v>
+        <v>78343</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3883,37 +3897,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494068</v>
+        <v>493790</v>
       </c>
       <c r="R33" t="n">
-        <v>6834592</v>
+        <v>6834696</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3942,7 +3956,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3952,7 +3966,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3967,22 +3981,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121461098</v>
+        <v>121460832</v>
       </c>
       <c r="B34" t="n">
-        <v>78604</v>
+        <v>79225</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3995,27 +4009,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
@@ -4054,7 +4068,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4064,7 +4078,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4084,17 +4098,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121463373</v>
+        <v>121462254</v>
       </c>
       <c r="B35" t="n">
-        <v>90675</v>
+        <v>98098</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4103,41 +4117,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494068</v>
+        <v>493917</v>
       </c>
       <c r="R35" t="n">
-        <v>6834592</v>
+        <v>6834563</v>
       </c>
       <c r="S35" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4164,19 +4178,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4191,22 +4195,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121463160</v>
+        <v>121462206</v>
       </c>
       <c r="B36" t="n">
-        <v>78605</v>
+        <v>78607</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4219,16 +4223,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4237,22 +4241,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barkheden, Barkheden, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494004</v>
+        <v>493812</v>
       </c>
       <c r="R36" t="n">
-        <v>6834553</v>
+        <v>6834571</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4281,7 +4282,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4291,7 +4292,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4300,29 +4301,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121462206</v>
+        <v>121461485</v>
       </c>
       <c r="B37" t="n">
-        <v>78604</v>
+        <v>79225</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4335,21 +4335,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4359,13 +4359,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493812</v>
+        <v>493825</v>
       </c>
       <c r="R37" t="n">
-        <v>6834571</v>
+        <v>6834542</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4419,22 +4419,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121463076</v>
+        <v>121463373</v>
       </c>
       <c r="B38" t="n">
-        <v>74710</v>
+        <v>90678</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4443,25 +4443,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4471,13 +4471,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494009</v>
+        <v>494068</v>
       </c>
       <c r="R38" t="n">
-        <v>6834588</v>
+        <v>6834592</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4543,10 +4543,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121460788</v>
+        <v>121461117</v>
       </c>
       <c r="B39" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493790</v>
+        <v>493817</v>
       </c>
       <c r="R39" t="n">
-        <v>6834696</v>
+        <v>6834627</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4648,17 +4648,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121461485</v>
+        <v>121462937</v>
       </c>
       <c r="B40" t="n">
-        <v>79222</v>
+        <v>74713</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4671,21 +4671,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493825</v>
+        <v>494004</v>
       </c>
       <c r="R40" t="n">
-        <v>6834542</v>
+        <v>6834553</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121460831</v>
+        <v>121464008</v>
       </c>
       <c r="B41" t="n">
-        <v>78340</v>
+        <v>78344</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4783,37 +4783,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493790</v>
+        <v>494068</v>
       </c>
       <c r="R41" t="n">
-        <v>6834696</v>
+        <v>6834592</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4867,22 +4867,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121461113</v>
+        <v>121463076</v>
       </c>
       <c r="B42" t="n">
-        <v>78341</v>
+        <v>74713</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4895,37 +4895,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493790</v>
+        <v>494009</v>
       </c>
       <c r="R42" t="n">
-        <v>6834696</v>
+        <v>6834588</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4979,22 +4979,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121463131</v>
+        <v>121463743</v>
       </c>
       <c r="B43" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494081</v>
+        <v>494116</v>
       </c>
       <c r="R43" t="n">
-        <v>6834614</v>
+        <v>6834573</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5116,10 +5116,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121463743</v>
+        <v>121463365</v>
       </c>
       <c r="B44" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5168,10 +5168,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494116</v>
+        <v>494086</v>
       </c>
       <c r="R44" t="n">
-        <v>6834573</v>
+        <v>6834603</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5241,10 +5241,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121463365</v>
+        <v>121463131</v>
       </c>
       <c r="B45" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494086</v>
+        <v>494081</v>
       </c>
       <c r="R45" t="n">
-        <v>6834603</v>
+        <v>6834614</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5366,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121462195</v>
+        <v>121462959</v>
       </c>
       <c r="B46" t="n">
-        <v>57504</v>
+        <v>98098</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5378,38 +5378,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493861</v>
+        <v>494001</v>
       </c>
       <c r="R46" t="n">
-        <v>6834554</v>
+        <v>6834589</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5441,7 +5450,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5451,7 +5460,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5478,10 +5487,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121463429</v>
+        <v>121461167</v>
       </c>
       <c r="B47" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5518,10 +5527,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494075</v>
+        <v>493883</v>
       </c>
       <c r="R47" t="n">
-        <v>6834606</v>
+        <v>6834518</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5553,7 +5562,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5563,12 +5572,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På Tallstamnen</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5598,7 +5607,7 @@
         <v>121462834</v>
       </c>
       <c r="B48" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5712,10 +5721,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121462243</v>
+        <v>121463067</v>
       </c>
       <c r="B49" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5752,10 +5761,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493905</v>
+        <v>493995</v>
       </c>
       <c r="R49" t="n">
-        <v>6834568</v>
+        <v>6834619</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -5787,7 +5796,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5797,7 +5806,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Gran och tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5824,10 +5838,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121461167</v>
+        <v>121463770</v>
       </c>
       <c r="B50" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5864,10 +5878,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493883</v>
+        <v>494125</v>
       </c>
       <c r="R50" t="n">
-        <v>6834518</v>
+        <v>6834588</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -5899,7 +5913,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5909,12 +5923,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På Tallstamnen</t>
+          <t>Tallstam</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5941,10 +5955,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121463770</v>
+        <v>121463429</v>
       </c>
       <c r="B51" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5981,10 +5995,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494125</v>
+        <v>494075</v>
       </c>
       <c r="R51" t="n">
-        <v>6834588</v>
+        <v>6834606</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6016,7 +6030,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6026,12 +6040,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Tallstam</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6058,10 +6072,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121461118</v>
+        <v>121461121</v>
       </c>
       <c r="B52" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6091,26 +6105,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493869</v>
+        <v>493873</v>
       </c>
       <c r="R52" t="n">
-        <v>6834529</v>
+        <v>6834530</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6142,7 +6147,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6152,7 +6157,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6179,10 +6184,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121463067</v>
+        <v>121462195</v>
       </c>
       <c r="B53" t="n">
-        <v>78604</v>
+        <v>57507</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6195,34 +6200,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493995</v>
+        <v>493861</v>
       </c>
       <c r="R53" t="n">
-        <v>6834619</v>
+        <v>6834554</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6254,7 +6259,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6264,12 +6269,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Gran och tall</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6296,10 +6296,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121461121</v>
+        <v>121461118</v>
       </c>
       <c r="B54" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6329,17 +6329,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493873</v>
+        <v>493869</v>
       </c>
       <c r="R54" t="n">
-        <v>6834530</v>
+        <v>6834529</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6371,7 +6380,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6381,7 +6390,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6408,10 +6417,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121462959</v>
+        <v>121462243</v>
       </c>
       <c r="B55" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6420,47 +6429,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494001</v>
+        <v>493905</v>
       </c>
       <c r="R55" t="n">
-        <v>6834589</v>
+        <v>6834568</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121316463</v>
+        <v>121313238</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493838</v>
+        <v>493815</v>
       </c>
       <c r="R2" t="n">
-        <v>6834855</v>
+        <v>6834929</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121314972</v>
+        <v>121314297</v>
       </c>
       <c r="B3" t="n">
         <v>98098</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493938</v>
+        <v>493861</v>
       </c>
       <c r="R3" t="n">
-        <v>6834637</v>
+        <v>6834789</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121314297</v>
+        <v>121314365</v>
       </c>
       <c r="B4" t="n">
         <v>98098</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493861</v>
+        <v>493868</v>
       </c>
       <c r="R4" t="n">
-        <v>6834789</v>
+        <v>6834817</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121316014</v>
+        <v>121316679</v>
       </c>
       <c r="B5" t="n">
         <v>98098</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493896</v>
+        <v>493815</v>
       </c>
       <c r="R5" t="n">
-        <v>6834747</v>
+        <v>6834794</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121314203</v>
+        <v>121313133</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493870</v>
+        <v>493849</v>
       </c>
       <c r="R6" t="n">
-        <v>6834767</v>
+        <v>6834871</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1159,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121313238</v>
+        <v>121313915</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493815</v>
+        <v>493790</v>
       </c>
       <c r="R7" t="n">
-        <v>6834929</v>
+        <v>6834789</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121314284</v>
+        <v>121316297</v>
       </c>
       <c r="B8" t="n">
         <v>98098</v>
@@ -1327,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493876</v>
+        <v>493886</v>
       </c>
       <c r="R8" t="n">
-        <v>6834703</v>
+        <v>6834817</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,19 +1382,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121313925</v>
+        <v>121316463</v>
       </c>
       <c r="B9" t="n">
         <v>98098</v>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493790</v>
+        <v>493838</v>
       </c>
       <c r="R9" t="n">
-        <v>6834794</v>
+        <v>6834855</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1479,19 +1484,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121316126</v>
+        <v>121315050</v>
       </c>
       <c r="B10" t="n">
         <v>98098</v>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493898</v>
+        <v>493937</v>
       </c>
       <c r="R10" t="n">
-        <v>6834798</v>
+        <v>6834639</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121316548</v>
+        <v>121314203</v>
       </c>
       <c r="B11" t="n">
         <v>98098</v>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493794</v>
+        <v>493870</v>
       </c>
       <c r="R11" t="n">
-        <v>6834804</v>
+        <v>6834767</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121314027</v>
+        <v>121314269</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493811</v>
+        <v>493864</v>
       </c>
       <c r="R12" t="n">
-        <v>6834771</v>
+        <v>6834781</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1785,19 +1790,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121313915</v>
+        <v>121314211</v>
       </c>
       <c r="B13" t="n">
         <v>98098</v>
@@ -1837,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493790</v>
+        <v>493820</v>
       </c>
       <c r="R13" t="n">
-        <v>6834789</v>
+        <v>6834777</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1887,19 +1892,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121314199</v>
+        <v>121315885</v>
       </c>
       <c r="B14" t="n">
         <v>98098</v>
@@ -1939,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493816</v>
+        <v>493917</v>
       </c>
       <c r="R14" t="n">
-        <v>6834773</v>
+        <v>6834746</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1989,19 +1994,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121315885</v>
+        <v>121314344</v>
       </c>
       <c r="B15" t="n">
         <v>98098</v>
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493917</v>
+        <v>493875</v>
       </c>
       <c r="R15" t="n">
-        <v>6834746</v>
+        <v>6834814</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2103,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121313317</v>
+        <v>121314027</v>
       </c>
       <c r="B16" t="n">
-        <v>79717</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493813</v>
+        <v>493811</v>
       </c>
       <c r="R16" t="n">
-        <v>6834953</v>
+        <v>6834771</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2205,7 +2210,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121314365</v>
+        <v>121316014</v>
       </c>
       <c r="B17" t="n">
         <v>98098</v>
@@ -2245,13 +2250,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493868</v>
+        <v>493896</v>
       </c>
       <c r="R17" t="n">
-        <v>6834817</v>
+        <v>6834747</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2307,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121315050</v>
+        <v>121313317</v>
       </c>
       <c r="B18" t="n">
-        <v>98098</v>
+        <v>79717</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493937</v>
+        <v>493813</v>
       </c>
       <c r="R18" t="n">
-        <v>6834639</v>
+        <v>6834953</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2397,19 +2402,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121314344</v>
+        <v>121316126</v>
       </c>
       <c r="B19" t="n">
         <v>98098</v>
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493875</v>
+        <v>493898</v>
       </c>
       <c r="R19" t="n">
-        <v>6834814</v>
+        <v>6834798</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2511,7 +2516,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121316066</v>
+        <v>121316610</v>
       </c>
       <c r="B20" t="n">
         <v>98098</v>
@@ -2551,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493896</v>
+        <v>493818</v>
       </c>
       <c r="R20" t="n">
-        <v>6834749</v>
+        <v>6834795</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2613,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121314211</v>
+        <v>121314407</v>
       </c>
       <c r="B21" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,13 +2658,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493820</v>
+        <v>493810</v>
       </c>
       <c r="R21" t="n">
-        <v>6834777</v>
+        <v>6834885</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2703,19 +2708,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121314269</v>
+        <v>121313925</v>
       </c>
       <c r="B22" t="n">
         <v>98098</v>
@@ -2755,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493864</v>
+        <v>493790</v>
       </c>
       <c r="R22" t="n">
-        <v>6834781</v>
+        <v>6834794</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2805,19 +2810,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121316297</v>
+        <v>121316066</v>
       </c>
       <c r="B23" t="n">
         <v>98098</v>
@@ -2857,13 +2862,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493886</v>
+        <v>493896</v>
       </c>
       <c r="R23" t="n">
-        <v>6834817</v>
+        <v>6834749</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2919,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121316610</v>
+        <v>121313741</v>
       </c>
       <c r="B24" t="n">
-        <v>98098</v>
+        <v>57507</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2931,25 +2936,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,13 +2964,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493818</v>
+        <v>493766</v>
       </c>
       <c r="R24" t="n">
-        <v>6834795</v>
+        <v>6834823</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2995,6 +3000,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3009,12 +3019,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3123,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121313741</v>
+        <v>121316548</v>
       </c>
       <c r="B26" t="n">
-        <v>57507</v>
+        <v>98098</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3135,25 +3145,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,13 +3173,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493766</v>
+        <v>493794</v>
       </c>
       <c r="R26" t="n">
-        <v>6834823</v>
+        <v>6834804</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3199,11 +3209,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3218,22 +3223,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121314407</v>
+        <v>121314284</v>
       </c>
       <c r="B27" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,25 +3247,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3270,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493810</v>
+        <v>493876</v>
       </c>
       <c r="R27" t="n">
-        <v>6834885</v>
+        <v>6834703</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3320,22 +3325,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121313133</v>
+        <v>121314199</v>
       </c>
       <c r="B28" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,25 +3349,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493849</v>
+        <v>493816</v>
       </c>
       <c r="R28" t="n">
-        <v>6834871</v>
+        <v>6834773</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3410,11 +3415,6 @@
           <t>2024-11-23</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På rönn</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3427,19 +3427,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121316679</v>
+        <v>121314972</v>
       </c>
       <c r="B29" t="n">
         <v>98098</v>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493815</v>
+        <v>493938</v>
       </c>
       <c r="R29" t="n">
-        <v>6834794</v>
+        <v>6834637</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121463160</v>
+        <v>121462206</v>
       </c>
       <c r="B30" t="n">
-        <v>78608</v>
+        <v>78607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,16 +3557,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3575,22 +3575,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Barkheden, Barkheden, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494004</v>
+        <v>493812</v>
       </c>
       <c r="R30" t="n">
-        <v>6834553</v>
+        <v>6834571</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3619,7 +3616,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3629,7 +3626,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3638,29 +3635,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121461098</v>
+        <v>121462937</v>
       </c>
       <c r="B31" t="n">
-        <v>78607</v>
+        <v>74713</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3673,21 +3669,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3697,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493790</v>
+        <v>494004</v>
       </c>
       <c r="R31" t="n">
-        <v>6834696</v>
+        <v>6834553</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3732,7 +3728,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3742,7 +3738,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3762,17 +3758,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121461113</v>
+        <v>121460832</v>
       </c>
       <c r="B32" t="n">
-        <v>78344</v>
+        <v>79225</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3785,27 +3781,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -3844,7 +3840,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3854,7 +3850,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3881,10 +3877,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121460831</v>
+        <v>121461113</v>
       </c>
       <c r="B33" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3897,27 +3893,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -3956,7 +3952,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3966,7 +3962,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3993,10 +3989,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121460832</v>
+        <v>121463373</v>
       </c>
       <c r="B34" t="n">
-        <v>79225</v>
+        <v>90678</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4005,41 +4001,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493790</v>
+        <v>494068</v>
       </c>
       <c r="R34" t="n">
-        <v>6834696</v>
+        <v>6834592</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4068,7 +4064,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4078,7 +4074,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4093,22 +4089,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121462254</v>
+        <v>121461485</v>
       </c>
       <c r="B35" t="n">
-        <v>98098</v>
+        <v>79225</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4117,41 +4113,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493917</v>
+        <v>493825</v>
       </c>
       <c r="R35" t="n">
-        <v>6834563</v>
+        <v>6834542</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4178,9 +4174,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4195,22 +4201,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121462206</v>
+        <v>121460831</v>
       </c>
       <c r="B36" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4223,37 +4229,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493812</v>
+        <v>493790</v>
       </c>
       <c r="R36" t="n">
-        <v>6834571</v>
+        <v>6834696</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4282,7 +4288,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4292,7 +4298,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4307,19 +4313,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121461485</v>
+        <v>121461117</v>
       </c>
       <c r="B37" t="n">
         <v>79225</v>
@@ -4359,10 +4365,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493825</v>
+        <v>493817</v>
       </c>
       <c r="R37" t="n">
-        <v>6834542</v>
+        <v>6834627</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4394,7 +4400,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4404,7 +4410,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4431,10 +4437,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121463373</v>
+        <v>121463076</v>
       </c>
       <c r="B38" t="n">
-        <v>90678</v>
+        <v>74713</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4443,25 +4449,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4471,13 +4477,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494068</v>
+        <v>494009</v>
       </c>
       <c r="R38" t="n">
-        <v>6834592</v>
+        <v>6834588</v>
       </c>
       <c r="S38" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4506,7 +4512,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4516,7 +4522,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4543,10 +4549,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121461117</v>
+        <v>121461098</v>
       </c>
       <c r="B39" t="n">
-        <v>79225</v>
+        <v>78607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4559,21 +4565,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4583,10 +4589,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493817</v>
+        <v>493790</v>
       </c>
       <c r="R39" t="n">
-        <v>6834627</v>
+        <v>6834696</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4618,7 +4624,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4628,7 +4634,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4655,10 +4661,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121462937</v>
+        <v>121464008</v>
       </c>
       <c r="B40" t="n">
-        <v>74713</v>
+        <v>78344</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4671,37 +4677,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494004</v>
+        <v>494068</v>
       </c>
       <c r="R40" t="n">
-        <v>6834553</v>
+        <v>6834592</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4730,7 +4736,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4740,7 +4746,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4755,22 +4761,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121464008</v>
+        <v>121462254</v>
       </c>
       <c r="B41" t="n">
-        <v>78344</v>
+        <v>98098</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4779,41 +4785,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494068</v>
+        <v>493917</v>
       </c>
       <c r="R41" t="n">
-        <v>6834592</v>
+        <v>6834563</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4840,19 +4846,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4867,22 +4863,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121463076</v>
+        <v>121463160</v>
       </c>
       <c r="B42" t="n">
-        <v>74713</v>
+        <v>78608</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4895,37 +4891,40 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>230405</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Barkheden, Barkheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494009</v>
+        <v>494004</v>
       </c>
       <c r="R42" t="n">
-        <v>6834588</v>
+        <v>6834553</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4954,7 +4953,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4964,7 +4963,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4973,25 +4972,26 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121463743</v>
+        <v>121463131</v>
       </c>
       <c r="B43" t="n">
         <v>98098</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494116</v>
+        <v>494081</v>
       </c>
       <c r="R43" t="n">
-        <v>6834573</v>
+        <v>6834614</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5116,7 +5116,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121463365</v>
+        <v>121463743</v>
       </c>
       <c r="B44" t="n">
         <v>98098</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5168,10 +5168,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494086</v>
+        <v>494116</v>
       </c>
       <c r="R44" t="n">
-        <v>6834603</v>
+        <v>6834573</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5241,7 +5241,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121463131</v>
+        <v>121463365</v>
       </c>
       <c r="B45" t="n">
         <v>98098</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494081</v>
+        <v>494086</v>
       </c>
       <c r="R45" t="n">
-        <v>6834614</v>
+        <v>6834603</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5366,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121462959</v>
+        <v>121463067</v>
       </c>
       <c r="B46" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5378,47 +5378,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494001</v>
+        <v>493995</v>
       </c>
       <c r="R46" t="n">
-        <v>6834589</v>
+        <v>6834619</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5450,7 +5441,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5460,7 +5451,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gran och tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5487,10 +5483,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121461167</v>
+        <v>121461121</v>
       </c>
       <c r="B47" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5499,38 +5495,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493883</v>
+        <v>493873</v>
       </c>
       <c r="R47" t="n">
-        <v>6834518</v>
+        <v>6834530</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5573,11 +5569,6 @@
       <c r="AB47" t="inlineStr">
         <is>
           <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På Tallstamnen</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5604,10 +5595,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121462834</v>
+        <v>121462959</v>
       </c>
       <c r="B48" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5616,38 +5607,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494009</v>
+        <v>494001</v>
       </c>
       <c r="R48" t="n">
-        <v>6834570</v>
+        <v>6834589</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5689,12 +5689,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5721,10 +5716,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121463067</v>
+        <v>121461118</v>
       </c>
       <c r="B49" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5733,38 +5728,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493995</v>
+        <v>493869</v>
       </c>
       <c r="R49" t="n">
-        <v>6834619</v>
+        <v>6834529</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -5796,7 +5800,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5806,12 +5810,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Gran och tall</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5838,7 +5837,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121463770</v>
+        <v>121462834</v>
       </c>
       <c r="B50" t="n">
         <v>78607</v>
@@ -5878,10 +5877,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494125</v>
+        <v>494009</v>
       </c>
       <c r="R50" t="n">
-        <v>6834588</v>
+        <v>6834570</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -5913,7 +5912,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5923,12 +5922,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Tallstam</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6072,10 +6071,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121461121</v>
+        <v>121462243</v>
       </c>
       <c r="B52" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6084,38 +6083,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493873</v>
+        <v>493905</v>
       </c>
       <c r="R52" t="n">
-        <v>6834530</v>
+        <v>6834568</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6147,7 +6146,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6157,7 +6156,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6184,10 +6183,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121462195</v>
+        <v>121461167</v>
       </c>
       <c r="B53" t="n">
-        <v>57507</v>
+        <v>78607</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6200,34 +6199,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493861</v>
+        <v>493883</v>
       </c>
       <c r="R53" t="n">
-        <v>6834554</v>
+        <v>6834518</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6259,7 +6258,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6269,7 +6268,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På Tallstamnen</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6296,10 +6300,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121461118</v>
+        <v>121463770</v>
       </c>
       <c r="B54" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6308,47 +6312,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493869</v>
+        <v>494125</v>
       </c>
       <c r="R54" t="n">
-        <v>6834529</v>
+        <v>6834588</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6380,7 +6375,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6390,7 +6385,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Tallstam</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6417,10 +6417,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121462243</v>
+        <v>121462195</v>
       </c>
       <c r="B55" t="n">
-        <v>78607</v>
+        <v>57507</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6433,34 +6433,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493905</v>
+        <v>493861</v>
       </c>
       <c r="R55" t="n">
-        <v>6834568</v>
+        <v>6834554</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -5366,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121463067</v>
+        <v>121461121</v>
       </c>
       <c r="B46" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5378,38 +5378,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493995</v>
+        <v>493873</v>
       </c>
       <c r="R46" t="n">
-        <v>6834619</v>
+        <v>6834530</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5451,12 +5451,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gran och tall</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5483,10 +5478,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121461121</v>
+        <v>121463067</v>
       </c>
       <c r="B47" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5495,38 +5490,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493873</v>
+        <v>493995</v>
       </c>
       <c r="R47" t="n">
-        <v>6834530</v>
+        <v>6834619</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5558,7 +5553,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5568,7 +5563,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gran och tall</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121313238</v>
+        <v>121316463</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493815</v>
+        <v>493838</v>
       </c>
       <c r="R2" t="n">
-        <v>6834929</v>
+        <v>6834855</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121314297</v>
+        <v>121316548</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493861</v>
+        <v>493794</v>
       </c>
       <c r="R3" t="n">
-        <v>6834789</v>
+        <v>6834804</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121314365</v>
+        <v>121313238</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493868</v>
+        <v>493815</v>
       </c>
       <c r="R4" t="n">
-        <v>6834817</v>
+        <v>6834929</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121316679</v>
+        <v>121313915</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493815</v>
+        <v>493790</v>
       </c>
       <c r="R5" t="n">
-        <v>6834794</v>
+        <v>6834789</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121313133</v>
+        <v>121314297</v>
       </c>
       <c r="B6" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493849</v>
+        <v>493861</v>
       </c>
       <c r="R6" t="n">
-        <v>6834871</v>
+        <v>6834789</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1159,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121313915</v>
+        <v>121313925</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,10 +1228,10 @@
         <v>493790</v>
       </c>
       <c r="R7" t="n">
-        <v>6834789</v>
+        <v>6834794</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121316297</v>
+        <v>121314199</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493886</v>
+        <v>493816</v>
       </c>
       <c r="R8" t="n">
-        <v>6834817</v>
+        <v>6834773</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121316463</v>
+        <v>121316679</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493838</v>
+        <v>493815</v>
       </c>
       <c r="R9" t="n">
-        <v>6834855</v>
+        <v>6834794</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1499,7 +1494,7 @@
         <v>121315050</v>
       </c>
       <c r="B10" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121314203</v>
+        <v>121313317</v>
       </c>
       <c r="B11" t="n">
-        <v>98098</v>
+        <v>79718</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493870</v>
+        <v>493813</v>
       </c>
       <c r="R11" t="n">
-        <v>6834767</v>
+        <v>6834953</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1688,22 +1683,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121314269</v>
+        <v>121316126</v>
       </c>
       <c r="B12" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493864</v>
+        <v>493898</v>
       </c>
       <c r="R12" t="n">
-        <v>6834781</v>
+        <v>6834798</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121314211</v>
+        <v>121315452</v>
       </c>
       <c r="B13" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493820</v>
+        <v>494000</v>
       </c>
       <c r="R13" t="n">
-        <v>6834777</v>
+        <v>6834510</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,22 +1887,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121315885</v>
+        <v>121314365</v>
       </c>
       <c r="B14" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,13 +1939,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493917</v>
+        <v>493868</v>
       </c>
       <c r="R14" t="n">
-        <v>6834746</v>
+        <v>6834817</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121314344</v>
+        <v>121314972</v>
       </c>
       <c r="B15" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493875</v>
+        <v>493938</v>
       </c>
       <c r="R15" t="n">
-        <v>6834814</v>
+        <v>6834637</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121314027</v>
+        <v>121315885</v>
       </c>
       <c r="B16" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493811</v>
+        <v>493917</v>
       </c>
       <c r="R16" t="n">
-        <v>6834771</v>
+        <v>6834746</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2198,22 +2193,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121316014</v>
+        <v>121313133</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493896</v>
+        <v>493849</v>
       </c>
       <c r="R17" t="n">
-        <v>6834747</v>
+        <v>6834871</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2286,6 +2281,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121313317</v>
+        <v>121314407</v>
       </c>
       <c r="B18" t="n">
-        <v>79717</v>
+        <v>79689</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493813</v>
+        <v>493810</v>
       </c>
       <c r="R18" t="n">
-        <v>6834953</v>
+        <v>6834885</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2402,22 +2402,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121316126</v>
+        <v>121314211</v>
       </c>
       <c r="B19" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,13 +2454,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493898</v>
+        <v>493820</v>
       </c>
       <c r="R19" t="n">
-        <v>6834798</v>
+        <v>6834777</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2504,22 +2504,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121316610</v>
+        <v>121316297</v>
       </c>
       <c r="B20" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493818</v>
+        <v>493886</v>
       </c>
       <c r="R20" t="n">
-        <v>6834795</v>
+        <v>6834817</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121314407</v>
+        <v>121316066</v>
       </c>
       <c r="B21" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493810</v>
+        <v>493896</v>
       </c>
       <c r="R21" t="n">
-        <v>6834885</v>
+        <v>6834749</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121313925</v>
+        <v>121316014</v>
       </c>
       <c r="B22" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493790</v>
+        <v>493896</v>
       </c>
       <c r="R22" t="n">
-        <v>6834794</v>
+        <v>6834747</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2810,22 +2810,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121316066</v>
+        <v>121314344</v>
       </c>
       <c r="B23" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493896</v>
+        <v>493875</v>
       </c>
       <c r="R23" t="n">
-        <v>6834749</v>
+        <v>6834814</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2927,7 +2927,7 @@
         <v>121313741</v>
       </c>
       <c r="B24" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121315452</v>
+        <v>121316610</v>
       </c>
       <c r="B25" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3043,25 +3043,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494000</v>
+        <v>493818</v>
       </c>
       <c r="R25" t="n">
-        <v>6834510</v>
+        <v>6834795</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121316548</v>
+        <v>121314269</v>
       </c>
       <c r="B26" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493794</v>
+        <v>493864</v>
       </c>
       <c r="R26" t="n">
-        <v>6834804</v>
+        <v>6834781</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121314284</v>
+        <v>121314203</v>
       </c>
       <c r="B27" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493876</v>
+        <v>493870</v>
       </c>
       <c r="R27" t="n">
-        <v>6834703</v>
+        <v>6834767</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3325,22 +3325,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121314199</v>
+        <v>121314027</v>
       </c>
       <c r="B28" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3349,25 +3349,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493816</v>
+        <v>493811</v>
       </c>
       <c r="R28" t="n">
-        <v>6834773</v>
+        <v>6834771</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121314972</v>
+        <v>121314284</v>
       </c>
       <c r="B29" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493938</v>
+        <v>493876</v>
       </c>
       <c r="R29" t="n">
-        <v>6834637</v>
+        <v>6834703</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3529,22 +3529,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121462206</v>
+        <v>121460831</v>
       </c>
       <c r="B30" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,37 +3557,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493812</v>
+        <v>493790</v>
       </c>
       <c r="R30" t="n">
-        <v>6834571</v>
+        <v>6834696</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3641,22 +3641,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121462937</v>
+        <v>121461098</v>
       </c>
       <c r="B31" t="n">
-        <v>74713</v>
+        <v>78608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3669,21 +3669,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494004</v>
+        <v>493790</v>
       </c>
       <c r="R31" t="n">
-        <v>6834553</v>
+        <v>6834696</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121460832</v>
+        <v>121463373</v>
       </c>
       <c r="B32" t="n">
-        <v>79225</v>
+        <v>90684</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3777,41 +3777,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493790</v>
+        <v>494068</v>
       </c>
       <c r="R32" t="n">
-        <v>6834696</v>
+        <v>6834592</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,12 +3865,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3880,7 +3880,7 @@
         <v>121461113</v>
       </c>
       <c r="B33" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121463373</v>
+        <v>121462206</v>
       </c>
       <c r="B34" t="n">
-        <v>90678</v>
+        <v>78608</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4001,41 +4001,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494068</v>
+        <v>493812</v>
       </c>
       <c r="R34" t="n">
-        <v>6834592</v>
+        <v>6834571</v>
       </c>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4104,7 +4104,7 @@
         <v>121461485</v>
       </c>
       <c r="B35" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4213,10 +4213,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121460831</v>
+        <v>121464008</v>
       </c>
       <c r="B36" t="n">
-        <v>78343</v>
+        <v>78345</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4229,37 +4229,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493790</v>
+        <v>494068</v>
       </c>
       <c r="R36" t="n">
-        <v>6834696</v>
+        <v>6834592</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4313,22 +4313,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121461117</v>
+        <v>121462937</v>
       </c>
       <c r="B37" t="n">
-        <v>79225</v>
+        <v>74714</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4341,21 +4341,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493817</v>
+        <v>494004</v>
       </c>
       <c r="R37" t="n">
-        <v>6834627</v>
+        <v>6834553</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4430,17 +4430,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121463076</v>
+        <v>121462254</v>
       </c>
       <c r="B38" t="n">
-        <v>74713</v>
+        <v>98104</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4449,41 +4449,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494009</v>
+        <v>493917</v>
       </c>
       <c r="R38" t="n">
-        <v>6834588</v>
+        <v>6834563</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4510,19 +4510,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4537,22 +4527,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121461098</v>
+        <v>121460788</v>
       </c>
       <c r="B39" t="n">
-        <v>78607</v>
+        <v>79226</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4565,21 +4555,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4624,7 +4614,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4634,7 +4624,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4654,17 +4644,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121464008</v>
+        <v>121461165</v>
       </c>
       <c r="B40" t="n">
-        <v>78344</v>
+        <v>79226</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4677,37 +4667,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494068</v>
+        <v>493817</v>
       </c>
       <c r="R40" t="n">
-        <v>6834592</v>
+        <v>6834627</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4736,7 +4726,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4746,7 +4736,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4761,22 +4751,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121462254</v>
+        <v>121463160</v>
       </c>
       <c r="B41" t="n">
-        <v>98098</v>
+        <v>78609</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4785,41 +4775,44 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>230405</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Barkheden, Barkheden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493917</v>
+        <v>494004</v>
       </c>
       <c r="R41" t="n">
-        <v>6834563</v>
+        <v>6834553</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4846,39 +4839,50 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121463160</v>
+        <v>121463076</v>
       </c>
       <c r="B42" t="n">
-        <v>78608</v>
+        <v>74714</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4891,40 +4895,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>230405</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Barkheden, Barkheden, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494004</v>
+        <v>494009</v>
       </c>
       <c r="R42" t="n">
-        <v>6834553</v>
+        <v>6834588</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4953,7 +4954,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4963,7 +4964,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4972,29 +4973,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121463131</v>
+        <v>121463743</v>
       </c>
       <c r="B43" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494081</v>
+        <v>494116</v>
       </c>
       <c r="R43" t="n">
-        <v>6834614</v>
+        <v>6834573</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5116,10 +5116,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121463743</v>
+        <v>121463365</v>
       </c>
       <c r="B44" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5168,10 +5168,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494116</v>
+        <v>494086</v>
       </c>
       <c r="R44" t="n">
-        <v>6834573</v>
+        <v>6834603</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5241,10 +5241,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121463365</v>
+        <v>121463131</v>
       </c>
       <c r="B45" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494086</v>
+        <v>494081</v>
       </c>
       <c r="R45" t="n">
-        <v>6834603</v>
+        <v>6834614</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5366,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121461121</v>
+        <v>121463770</v>
       </c>
       <c r="B46" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5378,38 +5378,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493873</v>
+        <v>494125</v>
       </c>
       <c r="R46" t="n">
-        <v>6834530</v>
+        <v>6834588</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5451,7 +5451,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Tallstam</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5478,10 +5483,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121463067</v>
+        <v>121462195</v>
       </c>
       <c r="B47" t="n">
-        <v>78607</v>
+        <v>57508</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5494,34 +5499,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493995</v>
+        <v>493861</v>
       </c>
       <c r="R47" t="n">
-        <v>6834619</v>
+        <v>6834554</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5553,7 +5558,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5563,12 +5568,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Gran och tall</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5595,10 +5595,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121462959</v>
+        <v>121461118</v>
       </c>
       <c r="B48" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5640,14 +5640,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494001</v>
+        <v>493869</v>
       </c>
       <c r="R48" t="n">
-        <v>6834589</v>
+        <v>6834529</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5716,10 +5716,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121461118</v>
+        <v>121461121</v>
       </c>
       <c r="B49" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5749,26 +5749,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493869</v>
+        <v>493873</v>
       </c>
       <c r="R49" t="n">
-        <v>6834529</v>
+        <v>6834530</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -5800,7 +5791,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5810,7 +5801,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5840,7 +5831,7 @@
         <v>121462834</v>
       </c>
       <c r="B50" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5954,10 +5945,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121463429</v>
+        <v>121462959</v>
       </c>
       <c r="B51" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5966,38 +5957,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494075</v>
+        <v>494001</v>
       </c>
       <c r="R51" t="n">
-        <v>6834606</v>
+        <v>6834589</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6039,12 +6039,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6071,10 +6066,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121462243</v>
+        <v>121463067</v>
       </c>
       <c r="B52" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6111,10 +6106,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493905</v>
+        <v>493995</v>
       </c>
       <c r="R52" t="n">
-        <v>6834568</v>
+        <v>6834619</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6146,7 +6141,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6156,7 +6151,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gran och tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6183,10 +6183,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121461167</v>
+        <v>121462243</v>
       </c>
       <c r="B53" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493883</v>
+        <v>493905</v>
       </c>
       <c r="R53" t="n">
-        <v>6834518</v>
+        <v>6834568</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6268,12 +6268,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På Tallstamnen</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6300,10 +6295,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121463770</v>
+        <v>121461167</v>
       </c>
       <c r="B54" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6340,10 +6335,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494125</v>
+        <v>493883</v>
       </c>
       <c r="R54" t="n">
-        <v>6834588</v>
+        <v>6834518</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6375,7 +6370,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6385,12 +6380,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Tallstam</t>
+          <t>På Tallstamnen</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6417,10 +6412,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121462195</v>
+        <v>121463429</v>
       </c>
       <c r="B55" t="n">
-        <v>57507</v>
+        <v>78608</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6433,34 +6428,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493861</v>
+        <v>494075</v>
       </c>
       <c r="R55" t="n">
-        <v>6834554</v>
+        <v>6834606</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6492,7 +6487,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6502,7 +6497,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121313238</v>
+        <v>121313915</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>98104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493815</v>
+        <v>493790</v>
       </c>
       <c r="R4" t="n">
-        <v>6834929</v>
+        <v>6834789</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121313915</v>
+        <v>121313238</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493790</v>
+        <v>493815</v>
       </c>
       <c r="R5" t="n">
-        <v>6834789</v>
+        <v>6834929</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121316463</v>
+        <v>121316126</v>
       </c>
       <c r="B2" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493838</v>
+        <v>493898</v>
       </c>
       <c r="R2" t="n">
-        <v>6834855</v>
+        <v>6834798</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121316548</v>
+        <v>121314199</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493794</v>
+        <v>493816</v>
       </c>
       <c r="R3" t="n">
-        <v>6834804</v>
+        <v>6834773</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>121313915</v>
       </c>
       <c r="B4" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121313238</v>
+        <v>121316066</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493815</v>
+        <v>493896</v>
       </c>
       <c r="R5" t="n">
-        <v>6834929</v>
+        <v>6834749</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121314297</v>
+        <v>121315050</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493861</v>
+        <v>493937</v>
       </c>
       <c r="R6" t="n">
-        <v>6834789</v>
+        <v>6834639</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121313925</v>
+        <v>121314365</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493790</v>
+        <v>493868</v>
       </c>
       <c r="R7" t="n">
-        <v>6834794</v>
+        <v>6834817</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121314199</v>
+        <v>121316463</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493816</v>
+        <v>493838</v>
       </c>
       <c r="R8" t="n">
-        <v>6834773</v>
+        <v>6834855</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121316679</v>
+        <v>121313317</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>79719</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493815</v>
+        <v>493813</v>
       </c>
       <c r="R9" t="n">
-        <v>6834794</v>
+        <v>6834953</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121315050</v>
+        <v>121314344</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493937</v>
+        <v>493875</v>
       </c>
       <c r="R10" t="n">
-        <v>6834639</v>
+        <v>6834814</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121313317</v>
+        <v>121314407</v>
       </c>
       <c r="B11" t="n">
-        <v>79718</v>
+        <v>79690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493813</v>
+        <v>493810</v>
       </c>
       <c r="R11" t="n">
-        <v>6834953</v>
+        <v>6834885</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1683,22 +1683,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121316126</v>
+        <v>121316610</v>
       </c>
       <c r="B12" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493898</v>
+        <v>493818</v>
       </c>
       <c r="R12" t="n">
-        <v>6834798</v>
+        <v>6834795</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121315452</v>
+        <v>121315885</v>
       </c>
       <c r="B13" t="n">
-        <v>79689</v>
+        <v>98105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494000</v>
+        <v>493917</v>
       </c>
       <c r="R13" t="n">
-        <v>6834510</v>
+        <v>6834746</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121314365</v>
+        <v>121315452</v>
       </c>
       <c r="B14" t="n">
-        <v>98104</v>
+        <v>79690</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493868</v>
+        <v>494000</v>
       </c>
       <c r="R14" t="n">
-        <v>6834817</v>
+        <v>6834510</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>121314972</v>
       </c>
       <c r="B15" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121315885</v>
+        <v>121314203</v>
       </c>
       <c r="B16" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493917</v>
+        <v>493870</v>
       </c>
       <c r="R16" t="n">
-        <v>6834746</v>
+        <v>6834767</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121313133</v>
+        <v>121316014</v>
       </c>
       <c r="B17" t="n">
-        <v>79689</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493849</v>
+        <v>493896</v>
       </c>
       <c r="R17" t="n">
-        <v>6834871</v>
+        <v>6834747</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2281,11 +2281,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121314407</v>
+        <v>121314027</v>
       </c>
       <c r="B18" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493810</v>
+        <v>493811</v>
       </c>
       <c r="R18" t="n">
-        <v>6834885</v>
+        <v>6834771</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2402,22 +2397,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121314211</v>
+        <v>121313133</v>
       </c>
       <c r="B19" t="n">
-        <v>98104</v>
+        <v>79690</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,13 +2449,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493820</v>
+        <v>493849</v>
       </c>
       <c r="R19" t="n">
-        <v>6834777</v>
+        <v>6834871</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2490,6 +2485,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2504,22 +2504,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121316297</v>
+        <v>121313741</v>
       </c>
       <c r="B20" t="n">
-        <v>98104</v>
+        <v>57509</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493886</v>
+        <v>493766</v>
       </c>
       <c r="R20" t="n">
-        <v>6834817</v>
+        <v>6834823</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2592,6 +2592,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2606,22 +2611,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121316066</v>
+        <v>121313925</v>
       </c>
       <c r="B21" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2658,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493896</v>
+        <v>493790</v>
       </c>
       <c r="R21" t="n">
-        <v>6834749</v>
+        <v>6834794</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2708,22 +2713,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121316014</v>
+        <v>121316679</v>
       </c>
       <c r="B22" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2760,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493896</v>
+        <v>493815</v>
       </c>
       <c r="R22" t="n">
-        <v>6834747</v>
+        <v>6834794</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2822,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121314344</v>
+        <v>121314211</v>
       </c>
       <c r="B23" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,13 +2867,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493875</v>
+        <v>493820</v>
       </c>
       <c r="R23" t="n">
-        <v>6834814</v>
+        <v>6834777</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2912,22 +2917,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121313741</v>
+        <v>121316297</v>
       </c>
       <c r="B24" t="n">
-        <v>57508</v>
+        <v>98105</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,25 +2941,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,13 +2969,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493766</v>
+        <v>493886</v>
       </c>
       <c r="R24" t="n">
-        <v>6834823</v>
+        <v>6834817</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3000,11 +3005,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3019,22 +3019,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121316610</v>
+        <v>121314297</v>
       </c>
       <c r="B25" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3071,13 +3071,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493818</v>
+        <v>493861</v>
       </c>
       <c r="R25" t="n">
-        <v>6834795</v>
+        <v>6834789</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121314269</v>
+        <v>121316548</v>
       </c>
       <c r="B26" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493864</v>
+        <v>493794</v>
       </c>
       <c r="R26" t="n">
-        <v>6834781</v>
+        <v>6834804</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121314203</v>
+        <v>121314284</v>
       </c>
       <c r="B27" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493870</v>
+        <v>493876</v>
       </c>
       <c r="R27" t="n">
-        <v>6834767</v>
+        <v>6834703</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3325,22 +3325,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121314027</v>
+        <v>121313238</v>
       </c>
       <c r="B28" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3377,13 +3377,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493811</v>
+        <v>493815</v>
       </c>
       <c r="R28" t="n">
-        <v>6834771</v>
+        <v>6834929</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3427,22 +3427,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121314284</v>
+        <v>121314269</v>
       </c>
       <c r="B29" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493876</v>
+        <v>493864</v>
       </c>
       <c r="R29" t="n">
-        <v>6834703</v>
+        <v>6834781</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3529,22 +3529,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121460831</v>
+        <v>121460832</v>
       </c>
       <c r="B30" t="n">
-        <v>78344</v>
+        <v>79227</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121461098</v>
+        <v>121462254</v>
       </c>
       <c r="B31" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3665,41 +3665,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493790</v>
+        <v>493917</v>
       </c>
       <c r="R31" t="n">
-        <v>6834696</v>
+        <v>6834563</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3726,19 +3726,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>09:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3753,22 +3743,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121463373</v>
+        <v>121461485</v>
       </c>
       <c r="B32" t="n">
-        <v>90684</v>
+        <v>79227</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3777,41 +3767,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494068</v>
+        <v>493825</v>
       </c>
       <c r="R32" t="n">
-        <v>6834592</v>
+        <v>6834542</v>
       </c>
       <c r="S32" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3840,7 +3830,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3850,7 +3840,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,12 +3855,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3880,7 +3870,7 @@
         <v>121461113</v>
       </c>
       <c r="B33" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3989,10 +3979,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121462206</v>
+        <v>121462937</v>
       </c>
       <c r="B34" t="n">
-        <v>78608</v>
+        <v>74715</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4005,21 +3995,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4029,13 +4019,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493812</v>
+        <v>494004</v>
       </c>
       <c r="R34" t="n">
-        <v>6834571</v>
+        <v>6834553</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4064,7 +4054,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4074,7 +4064,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4089,22 +4079,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121461485</v>
+        <v>121462206</v>
       </c>
       <c r="B35" t="n">
-        <v>79226</v>
+        <v>78609</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4117,21 +4107,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4141,13 +4131,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493825</v>
+        <v>493812</v>
       </c>
       <c r="R35" t="n">
-        <v>6834542</v>
+        <v>6834571</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4176,7 +4166,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4186,7 +4176,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4201,22 +4191,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121464008</v>
+        <v>121461117</v>
       </c>
       <c r="B36" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4229,37 +4219,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494068</v>
+        <v>493817</v>
       </c>
       <c r="R36" t="n">
-        <v>6834592</v>
+        <v>6834627</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4288,7 +4278,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4298,7 +4288,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4313,22 +4303,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121462937</v>
+        <v>121463160</v>
       </c>
       <c r="B37" t="n">
-        <v>74714</v>
+        <v>78610</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4341,27 +4331,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>230405</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Barkheden, Barkheden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
@@ -4400,7 +4393,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4410,7 +4403,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4419,6 +4412,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4437,10 +4431,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121462254</v>
+        <v>121464008</v>
       </c>
       <c r="B38" t="n">
-        <v>98104</v>
+        <v>78346</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4449,41 +4443,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493917</v>
+        <v>494068</v>
       </c>
       <c r="R38" t="n">
-        <v>6834563</v>
+        <v>6834592</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4510,9 +4504,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4527,22 +4531,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121460788</v>
+        <v>121461098</v>
       </c>
       <c r="B39" t="n">
-        <v>79226</v>
+        <v>78609</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4555,21 +4559,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4614,7 +4618,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4624,7 +4628,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4644,17 +4648,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121461165</v>
+        <v>121463076</v>
       </c>
       <c r="B40" t="n">
-        <v>79226</v>
+        <v>74715</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4667,37 +4671,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493817</v>
+        <v>494009</v>
       </c>
       <c r="R40" t="n">
-        <v>6834627</v>
+        <v>6834588</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4726,7 +4730,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4736,7 +4740,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4751,22 +4755,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121463160</v>
+        <v>121463373</v>
       </c>
       <c r="B41" t="n">
-        <v>78609</v>
+        <v>90685</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4775,44 +4779,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>230405</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Barkheden, Barkheden, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494004</v>
+        <v>494068</v>
       </c>
       <c r="R41" t="n">
-        <v>6834553</v>
+        <v>6834592</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4841,7 +4842,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4851,7 +4852,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4860,29 +4861,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121463076</v>
+        <v>121460831</v>
       </c>
       <c r="B42" t="n">
-        <v>74714</v>
+        <v>78345</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4895,37 +4895,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494009</v>
+        <v>493790</v>
       </c>
       <c r="R42" t="n">
-        <v>6834588</v>
+        <v>6834696</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4979,22 +4979,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121463743</v>
+        <v>121463131</v>
       </c>
       <c r="B43" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494116</v>
+        <v>494081</v>
       </c>
       <c r="R43" t="n">
-        <v>6834573</v>
+        <v>6834614</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5119,7 +5119,7 @@
         <v>121463365</v>
       </c>
       <c r="B44" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121463131</v>
+        <v>121463743</v>
       </c>
       <c r="B45" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494081</v>
+        <v>494116</v>
       </c>
       <c r="R45" t="n">
-        <v>6834614</v>
+        <v>6834573</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5366,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121463770</v>
+        <v>121461121</v>
       </c>
       <c r="B46" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5378,38 +5378,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494125</v>
+        <v>493873</v>
       </c>
       <c r="R46" t="n">
-        <v>6834588</v>
+        <v>6834530</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5451,12 +5451,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Tallstam</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5483,10 +5478,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121462195</v>
+        <v>121463067</v>
       </c>
       <c r="B47" t="n">
-        <v>57508</v>
+        <v>78609</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5499,34 +5494,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493861</v>
+        <v>493995</v>
       </c>
       <c r="R47" t="n">
-        <v>6834554</v>
+        <v>6834619</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5558,7 +5553,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5568,7 +5563,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gran och tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5595,10 +5595,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121461118</v>
+        <v>121462243</v>
       </c>
       <c r="B48" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5607,47 +5607,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493869</v>
+        <v>493905</v>
       </c>
       <c r="R48" t="n">
-        <v>6834529</v>
+        <v>6834568</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5679,7 +5670,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5689,7 +5680,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5716,10 +5707,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121461121</v>
+        <v>121462834</v>
       </c>
       <c r="B49" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5728,38 +5719,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493873</v>
+        <v>494009</v>
       </c>
       <c r="R49" t="n">
-        <v>6834530</v>
+        <v>6834570</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -5791,7 +5782,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5801,7 +5792,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5828,10 +5824,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121462834</v>
+        <v>121462959</v>
       </c>
       <c r="B50" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5840,38 +5836,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494009</v>
+        <v>494001</v>
       </c>
       <c r="R50" t="n">
-        <v>6834570</v>
+        <v>6834589</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -5903,7 +5908,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5913,12 +5918,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5945,10 +5945,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121462959</v>
+        <v>121462195</v>
       </c>
       <c r="B51" t="n">
-        <v>98104</v>
+        <v>57509</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5957,47 +5957,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494001</v>
+        <v>493861</v>
       </c>
       <c r="R51" t="n">
-        <v>6834589</v>
+        <v>6834554</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6029,7 +6020,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6039,7 +6030,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6066,10 +6057,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121463067</v>
+        <v>121461167</v>
       </c>
       <c r="B52" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6106,10 +6097,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493995</v>
+        <v>493883</v>
       </c>
       <c r="R52" t="n">
-        <v>6834619</v>
+        <v>6834518</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6141,7 +6132,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6151,12 +6142,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Gran och tall</t>
+          <t>På Tallstamnen</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6183,10 +6174,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121462243</v>
+        <v>121463429</v>
       </c>
       <c r="B53" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6223,10 +6214,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493905</v>
+        <v>494075</v>
       </c>
       <c r="R53" t="n">
-        <v>6834568</v>
+        <v>6834606</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6258,7 +6249,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6268,7 +6259,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6295,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121461167</v>
+        <v>121461118</v>
       </c>
       <c r="B54" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6307,38 +6303,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493883</v>
+        <v>493869</v>
       </c>
       <c r="R54" t="n">
-        <v>6834518</v>
+        <v>6834529</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6370,7 +6375,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6380,12 +6385,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På Tallstamnen</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6412,10 +6412,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121463429</v>
+        <v>121463770</v>
       </c>
       <c r="B55" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6452,10 +6452,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494075</v>
+        <v>494125</v>
       </c>
       <c r="R55" t="n">
-        <v>6834606</v>
+        <v>6834588</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Tallstam</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121316126</v>
+        <v>121316548</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493898</v>
+        <v>493794</v>
       </c>
       <c r="R2" t="n">
-        <v>6834798</v>
+        <v>6834804</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121314199</v>
+        <v>121313133</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493816</v>
+        <v>493849</v>
       </c>
       <c r="R3" t="n">
-        <v>6834773</v>
+        <v>6834871</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -855,6 +855,11 @@
           <t>2024-11-23</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -867,19 +872,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121313915</v>
+        <v>121315885</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -919,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493790</v>
+        <v>493917</v>
       </c>
       <c r="R4" t="n">
-        <v>6834789</v>
+        <v>6834746</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1083,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121315050</v>
+        <v>121316679</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493937</v>
+        <v>493815</v>
       </c>
       <c r="R6" t="n">
-        <v>6834639</v>
+        <v>6834794</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121314365</v>
+        <v>121316610</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1225,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493868</v>
+        <v>493818</v>
       </c>
       <c r="R7" t="n">
-        <v>6834817</v>
+        <v>6834795</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121316463</v>
+        <v>121316014</v>
       </c>
       <c r="B8" t="n">
         <v>98105</v>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493838</v>
+        <v>493896</v>
       </c>
       <c r="R8" t="n">
-        <v>6834855</v>
+        <v>6834747</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121313317</v>
+        <v>121315452</v>
       </c>
       <c r="B9" t="n">
-        <v>79719</v>
+        <v>79690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493813</v>
+        <v>494000</v>
       </c>
       <c r="R9" t="n">
-        <v>6834953</v>
+        <v>6834510</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,22 +1484,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121314344</v>
+        <v>121314027</v>
       </c>
       <c r="B10" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493875</v>
+        <v>493811</v>
       </c>
       <c r="R10" t="n">
-        <v>6834814</v>
+        <v>6834771</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1581,22 +1586,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121314407</v>
+        <v>121314269</v>
       </c>
       <c r="B11" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493810</v>
+        <v>493864</v>
       </c>
       <c r="R11" t="n">
-        <v>6834885</v>
+        <v>6834781</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121316610</v>
+        <v>121313915</v>
       </c>
       <c r="B12" t="n">
         <v>98105</v>
@@ -1735,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493818</v>
+        <v>493790</v>
       </c>
       <c r="R12" t="n">
-        <v>6834795</v>
+        <v>6834789</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121315885</v>
+        <v>121314407</v>
       </c>
       <c r="B13" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493917</v>
+        <v>493810</v>
       </c>
       <c r="R13" t="n">
-        <v>6834746</v>
+        <v>6834885</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121315452</v>
+        <v>121313741</v>
       </c>
       <c r="B14" t="n">
-        <v>79690</v>
+        <v>57509</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494000</v>
+        <v>493766</v>
       </c>
       <c r="R14" t="n">
-        <v>6834510</v>
+        <v>6834823</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1975,6 +1980,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1989,19 +1999,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121314972</v>
+        <v>121316463</v>
       </c>
       <c r="B15" t="n">
         <v>98105</v>
@@ -2041,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493938</v>
+        <v>493838</v>
       </c>
       <c r="R15" t="n">
-        <v>6834637</v>
+        <v>6834855</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2103,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121314203</v>
+        <v>121314297</v>
       </c>
       <c r="B16" t="n">
         <v>98105</v>
@@ -2143,13 +2153,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493870</v>
+        <v>493861</v>
       </c>
       <c r="R16" t="n">
-        <v>6834767</v>
+        <v>6834789</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2205,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121316014</v>
+        <v>121315050</v>
       </c>
       <c r="B17" t="n">
         <v>98105</v>
@@ -2245,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493896</v>
+        <v>493937</v>
       </c>
       <c r="R17" t="n">
-        <v>6834747</v>
+        <v>6834639</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2307,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121314027</v>
+        <v>121314365</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2329,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,13 +2357,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493811</v>
+        <v>493868</v>
       </c>
       <c r="R18" t="n">
-        <v>6834771</v>
+        <v>6834817</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2397,22 +2407,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121313133</v>
+        <v>121316297</v>
       </c>
       <c r="B19" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2431,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,13 +2459,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493849</v>
+        <v>493886</v>
       </c>
       <c r="R19" t="n">
-        <v>6834871</v>
+        <v>6834817</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2485,11 +2495,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121313741</v>
+        <v>121314199</v>
       </c>
       <c r="B20" t="n">
-        <v>57509</v>
+        <v>98105</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2533,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,13 +2561,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493766</v>
+        <v>493816</v>
       </c>
       <c r="R20" t="n">
-        <v>6834823</v>
+        <v>6834773</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2592,11 +2597,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2623,7 +2623,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121313925</v>
+        <v>121314972</v>
       </c>
       <c r="B21" t="n">
         <v>98105</v>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493790</v>
+        <v>493938</v>
       </c>
       <c r="R21" t="n">
-        <v>6834794</v>
+        <v>6834637</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2713,19 +2713,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121316679</v>
+        <v>121314344</v>
       </c>
       <c r="B22" t="n">
         <v>98105</v>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493815</v>
+        <v>493875</v>
       </c>
       <c r="R22" t="n">
-        <v>6834794</v>
+        <v>6834814</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121314211</v>
+        <v>121313317</v>
       </c>
       <c r="B23" t="n">
-        <v>98105</v>
+        <v>79719</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2839,25 +2839,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,13 +2867,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493820</v>
+        <v>493813</v>
       </c>
       <c r="R23" t="n">
-        <v>6834777</v>
+        <v>6834953</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121316297</v>
+        <v>121313925</v>
       </c>
       <c r="B24" t="n">
         <v>98105</v>
@@ -2969,13 +2969,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493886</v>
+        <v>493790</v>
       </c>
       <c r="R24" t="n">
-        <v>6834817</v>
+        <v>6834794</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3019,19 +3019,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121314297</v>
+        <v>121316126</v>
       </c>
       <c r="B25" t="n">
         <v>98105</v>
@@ -3071,13 +3071,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493861</v>
+        <v>493898</v>
       </c>
       <c r="R25" t="n">
-        <v>6834789</v>
+        <v>6834798</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121316548</v>
+        <v>121313238</v>
       </c>
       <c r="B26" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3145,25 +3145,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493794</v>
+        <v>493815</v>
       </c>
       <c r="R26" t="n">
-        <v>6834804</v>
+        <v>6834929</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121313238</v>
+        <v>121314203</v>
       </c>
       <c r="B28" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3349,25 +3349,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,13 +3377,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493815</v>
+        <v>493870</v>
       </c>
       <c r="R28" t="n">
-        <v>6834929</v>
+        <v>6834767</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121314269</v>
+        <v>121314211</v>
       </c>
       <c r="B29" t="n">
         <v>98105</v>
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493864</v>
+        <v>493820</v>
       </c>
       <c r="R29" t="n">
-        <v>6834781</v>
+        <v>6834777</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3529,19 +3529,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121460832</v>
+        <v>121461165</v>
       </c>
       <c r="B30" t="n">
         <v>79227</v>
@@ -3577,14 +3577,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493790</v>
+        <v>493817</v>
       </c>
       <c r="R30" t="n">
-        <v>6834696</v>
+        <v>6834627</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3646,17 +3646,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121462254</v>
+        <v>121463160</v>
       </c>
       <c r="B31" t="n">
-        <v>98105</v>
+        <v>78610</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3665,41 +3665,44 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>230405</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Barkheden, Barkheden, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493917</v>
+        <v>494004</v>
       </c>
       <c r="R31" t="n">
-        <v>6834563</v>
+        <v>6834553</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3726,39 +3729,50 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121461485</v>
+        <v>121462254</v>
       </c>
       <c r="B32" t="n">
-        <v>79227</v>
+        <v>98105</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3767,41 +3781,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493825</v>
+        <v>493917</v>
       </c>
       <c r="R32" t="n">
-        <v>6834542</v>
+        <v>6834563</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3828,19 +3842,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3855,22 +3859,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121461113</v>
+        <v>121460832</v>
       </c>
       <c r="B33" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3883,27 +3887,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -3942,7 +3946,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3952,7 +3956,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3979,10 +3983,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121462937</v>
+        <v>121461098</v>
       </c>
       <c r="B34" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3995,21 +3999,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4019,10 +4023,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494004</v>
+        <v>493790</v>
       </c>
       <c r="R34" t="n">
-        <v>6834553</v>
+        <v>6834696</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4054,7 +4058,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4064,7 +4068,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4084,7 +4088,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4203,7 +4207,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121461117</v>
+        <v>121461485</v>
       </c>
       <c r="B36" t="n">
         <v>79227</v>
@@ -4243,10 +4247,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493817</v>
+        <v>493825</v>
       </c>
       <c r="R36" t="n">
-        <v>6834627</v>
+        <v>6834542</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4278,7 +4282,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4288,7 +4292,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4315,10 +4319,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121463160</v>
+        <v>121464008</v>
       </c>
       <c r="B37" t="n">
-        <v>78610</v>
+        <v>78346</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4331,40 +4335,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>230405</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Barkheden, Barkheden, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494004</v>
+        <v>494068</v>
       </c>
       <c r="R37" t="n">
-        <v>6834553</v>
+        <v>6834592</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4393,7 +4394,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4403,7 +4404,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4412,29 +4413,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121464008</v>
+        <v>121463076</v>
       </c>
       <c r="B38" t="n">
-        <v>78346</v>
+        <v>74715</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4447,21 +4447,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4471,13 +4471,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494068</v>
+        <v>494009</v>
       </c>
       <c r="R38" t="n">
-        <v>6834592</v>
+        <v>6834588</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4543,10 +4543,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121461098</v>
+        <v>121460831</v>
       </c>
       <c r="B39" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4559,27 +4559,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4648,14 +4648,14 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121463076</v>
+        <v>121462937</v>
       </c>
       <c r="B40" t="n">
         <v>74715</v>
@@ -4691,17 +4691,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494009</v>
+        <v>494004</v>
       </c>
       <c r="R40" t="n">
-        <v>6834588</v>
+        <v>6834553</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4755,22 +4755,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121463373</v>
+        <v>121461113</v>
       </c>
       <c r="B41" t="n">
-        <v>90685</v>
+        <v>78346</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4779,41 +4779,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494068</v>
+        <v>493790</v>
       </c>
       <c r="R41" t="n">
-        <v>6834592</v>
+        <v>6834696</v>
       </c>
       <c r="S41" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4867,22 +4867,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121460831</v>
+        <v>121463373</v>
       </c>
       <c r="B42" t="n">
-        <v>78345</v>
+        <v>90685</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4891,41 +4891,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493790</v>
+        <v>494068</v>
       </c>
       <c r="R42" t="n">
-        <v>6834696</v>
+        <v>6834592</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4979,19 +4979,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121463131</v>
+        <v>121463743</v>
       </c>
       <c r="B43" t="n">
         <v>98105</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494081</v>
+        <v>494116</v>
       </c>
       <c r="R43" t="n">
-        <v>6834614</v>
+        <v>6834573</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5116,7 +5116,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121463365</v>
+        <v>121463131</v>
       </c>
       <c r="B44" t="n">
         <v>98105</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5168,10 +5168,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494086</v>
+        <v>494081</v>
       </c>
       <c r="R44" t="n">
-        <v>6834603</v>
+        <v>6834614</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5241,7 +5241,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121463743</v>
+        <v>121463365</v>
       </c>
       <c r="B45" t="n">
         <v>98105</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494116</v>
+        <v>494086</v>
       </c>
       <c r="R45" t="n">
-        <v>6834573</v>
+        <v>6834603</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5366,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121461121</v>
+        <v>121462243</v>
       </c>
       <c r="B46" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5378,38 +5378,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493873</v>
+        <v>493905</v>
       </c>
       <c r="R46" t="n">
-        <v>6834530</v>
+        <v>6834568</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5478,7 +5478,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121463067</v>
+        <v>121463429</v>
       </c>
       <c r="B47" t="n">
         <v>78609</v>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493995</v>
+        <v>494075</v>
       </c>
       <c r="R47" t="n">
-        <v>6834619</v>
+        <v>6834606</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gran och tall</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5595,10 +5595,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121462243</v>
+        <v>121461118</v>
       </c>
       <c r="B48" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5607,38 +5607,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493905</v>
+        <v>493869</v>
       </c>
       <c r="R48" t="n">
-        <v>6834568</v>
+        <v>6834529</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5670,7 +5679,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5680,7 +5689,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5707,7 +5716,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121462834</v>
+        <v>121463770</v>
       </c>
       <c r="B49" t="n">
         <v>78609</v>
@@ -5747,10 +5756,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494009</v>
+        <v>494125</v>
       </c>
       <c r="R49" t="n">
-        <v>6834570</v>
+        <v>6834588</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -5782,7 +5791,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5792,12 +5801,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Tallstam</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5824,10 +5833,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121462959</v>
+        <v>121462834</v>
       </c>
       <c r="B50" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5836,47 +5845,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494001</v>
+        <v>494009</v>
       </c>
       <c r="R50" t="n">
-        <v>6834589</v>
+        <v>6834570</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5918,7 +5918,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5945,10 +5950,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121462195</v>
+        <v>121461167</v>
       </c>
       <c r="B51" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5961,34 +5966,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493861</v>
+        <v>493883</v>
       </c>
       <c r="R51" t="n">
-        <v>6834554</v>
+        <v>6834518</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6020,7 +6025,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6030,7 +6035,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På Tallstamnen</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6057,7 +6067,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121461167</v>
+        <v>121463067</v>
       </c>
       <c r="B52" t="n">
         <v>78609</v>
@@ -6097,10 +6107,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493883</v>
+        <v>493995</v>
       </c>
       <c r="R52" t="n">
-        <v>6834518</v>
+        <v>6834619</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6132,7 +6142,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6142,12 +6152,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På Tallstamnen</t>
+          <t>Gran och tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6174,10 +6184,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121463429</v>
+        <v>121462959</v>
       </c>
       <c r="B53" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6186,38 +6196,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494075</v>
+        <v>494001</v>
       </c>
       <c r="R53" t="n">
-        <v>6834606</v>
+        <v>6834589</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6249,7 +6268,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6259,12 +6278,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6291,7 +6305,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121461118</v>
+        <v>121461121</v>
       </c>
       <c r="B54" t="n">
         <v>98105</v>
@@ -6324,26 +6338,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493869</v>
+        <v>493873</v>
       </c>
       <c r="R54" t="n">
-        <v>6834529</v>
+        <v>6834530</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6375,7 +6380,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6385,7 +6390,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6412,10 +6417,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121463770</v>
+        <v>121462195</v>
       </c>
       <c r="B55" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6428,34 +6433,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494125</v>
+        <v>493861</v>
       </c>
       <c r="R55" t="n">
-        <v>6834588</v>
+        <v>6834554</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6487,7 +6492,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6497,12 +6502,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Tallstam</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121316548</v>
+        <v>121313925</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493794</v>
+        <v>493790</v>
       </c>
       <c r="R2" t="n">
-        <v>6834804</v>
+        <v>6834794</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121313133</v>
+        <v>121316066</v>
       </c>
       <c r="B3" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493849</v>
+        <v>493896</v>
       </c>
       <c r="R3" t="n">
-        <v>6834871</v>
+        <v>6834749</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121315885</v>
+        <v>121314972</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493917</v>
+        <v>493938</v>
       </c>
       <c r="R4" t="n">
-        <v>6834746</v>
+        <v>6834637</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121316066</v>
+        <v>121314297</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1026,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493896</v>
+        <v>493861</v>
       </c>
       <c r="R5" t="n">
-        <v>6834749</v>
+        <v>6834789</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121316679</v>
+        <v>121314027</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493815</v>
+        <v>493811</v>
       </c>
       <c r="R6" t="n">
-        <v>6834794</v>
+        <v>6834771</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1178,19 +1173,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121316610</v>
+        <v>121316463</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493818</v>
+        <v>493838</v>
       </c>
       <c r="R7" t="n">
-        <v>6834795</v>
+        <v>6834855</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121316014</v>
+        <v>121316548</v>
       </c>
       <c r="B8" t="n">
         <v>98105</v>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493896</v>
+        <v>493794</v>
       </c>
       <c r="R8" t="n">
-        <v>6834747</v>
+        <v>6834804</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121315452</v>
+        <v>121314269</v>
       </c>
       <c r="B9" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494000</v>
+        <v>493864</v>
       </c>
       <c r="R9" t="n">
-        <v>6834510</v>
+        <v>6834781</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121314027</v>
+        <v>121314407</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493811</v>
+        <v>493810</v>
       </c>
       <c r="R10" t="n">
-        <v>6834771</v>
+        <v>6834885</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1586,19 +1581,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121314269</v>
+        <v>121315050</v>
       </c>
       <c r="B11" t="n">
         <v>98105</v>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493864</v>
+        <v>493937</v>
       </c>
       <c r="R11" t="n">
-        <v>6834781</v>
+        <v>6834639</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121313915</v>
+        <v>121313238</v>
       </c>
       <c r="B12" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,13 +1735,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493790</v>
+        <v>493815</v>
       </c>
       <c r="R12" t="n">
-        <v>6834789</v>
+        <v>6834929</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121314407</v>
+        <v>121316297</v>
       </c>
       <c r="B13" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493810</v>
+        <v>493886</v>
       </c>
       <c r="R13" t="n">
-        <v>6834885</v>
+        <v>6834817</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121313741</v>
+        <v>121313133</v>
       </c>
       <c r="B14" t="n">
-        <v>57509</v>
+        <v>79690</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,13 +1939,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493766</v>
+        <v>493849</v>
       </c>
       <c r="R14" t="n">
-        <v>6834823</v>
+        <v>6834871</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1984,7 +1979,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Lockläte</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1999,19 +1994,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121316463</v>
+        <v>121314203</v>
       </c>
       <c r="B15" t="n">
         <v>98105</v>
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493838</v>
+        <v>493870</v>
       </c>
       <c r="R15" t="n">
-        <v>6834855</v>
+        <v>6834767</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2113,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121314297</v>
+        <v>121313317</v>
       </c>
       <c r="B16" t="n">
-        <v>98105</v>
+        <v>79719</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493861</v>
+        <v>493813</v>
       </c>
       <c r="R16" t="n">
-        <v>6834789</v>
+        <v>6834953</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2203,19 +2198,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121315050</v>
+        <v>121316014</v>
       </c>
       <c r="B17" t="n">
         <v>98105</v>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493937</v>
+        <v>493896</v>
       </c>
       <c r="R17" t="n">
-        <v>6834639</v>
+        <v>6834747</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2419,7 +2414,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121316297</v>
+        <v>121316610</v>
       </c>
       <c r="B19" t="n">
         <v>98105</v>
@@ -2459,13 +2454,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493886</v>
+        <v>493818</v>
       </c>
       <c r="R19" t="n">
-        <v>6834817</v>
+        <v>6834795</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2521,7 +2516,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121314199</v>
+        <v>121314344</v>
       </c>
       <c r="B20" t="n">
         <v>98105</v>
@@ -2561,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493816</v>
+        <v>493875</v>
       </c>
       <c r="R20" t="n">
-        <v>6834773</v>
+        <v>6834814</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2611,19 +2606,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121314972</v>
+        <v>121316126</v>
       </c>
       <c r="B21" t="n">
         <v>98105</v>
@@ -2663,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493938</v>
+        <v>493898</v>
       </c>
       <c r="R21" t="n">
-        <v>6834637</v>
+        <v>6834798</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2725,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121314344</v>
+        <v>121314199</v>
       </c>
       <c r="B22" t="n">
         <v>98105</v>
@@ -2765,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493875</v>
+        <v>493816</v>
       </c>
       <c r="R22" t="n">
-        <v>6834814</v>
+        <v>6834773</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2815,22 +2810,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121313317</v>
+        <v>121316679</v>
       </c>
       <c r="B23" t="n">
-        <v>79719</v>
+        <v>98105</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2839,25 +2834,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,13 +2862,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493813</v>
+        <v>493815</v>
       </c>
       <c r="R23" t="n">
-        <v>6834953</v>
+        <v>6834794</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2917,19 +2912,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121313925</v>
+        <v>121314284</v>
       </c>
       <c r="B24" t="n">
         <v>98105</v>
@@ -2969,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493790</v>
+        <v>493876</v>
       </c>
       <c r="R24" t="n">
-        <v>6834794</v>
+        <v>6834703</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3031,7 +3026,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121316126</v>
+        <v>121314211</v>
       </c>
       <c r="B25" t="n">
         <v>98105</v>
@@ -3071,13 +3066,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493898</v>
+        <v>493820</v>
       </c>
       <c r="R25" t="n">
-        <v>6834798</v>
+        <v>6834777</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3121,22 +3116,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121313238</v>
+        <v>121315452</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,13 +3168,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493815</v>
+        <v>494000</v>
       </c>
       <c r="R26" t="n">
-        <v>6834929</v>
+        <v>6834510</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3235,7 +3230,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121314284</v>
+        <v>121315885</v>
       </c>
       <c r="B27" t="n">
         <v>98105</v>
@@ -3275,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493876</v>
+        <v>493917</v>
       </c>
       <c r="R27" t="n">
-        <v>6834703</v>
+        <v>6834746</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3325,22 +3320,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121314203</v>
+        <v>121313741</v>
       </c>
       <c r="B28" t="n">
-        <v>98105</v>
+        <v>57509</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3349,25 +3344,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,13 +3372,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493870</v>
+        <v>493766</v>
       </c>
       <c r="R28" t="n">
-        <v>6834767</v>
+        <v>6834823</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3413,6 +3408,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3427,19 +3427,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121314211</v>
+        <v>121313915</v>
       </c>
       <c r="B29" t="n">
         <v>98105</v>
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493820</v>
+        <v>493790</v>
       </c>
       <c r="R29" t="n">
-        <v>6834777</v>
+        <v>6834789</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3529,22 +3529,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121461165</v>
+        <v>121462254</v>
       </c>
       <c r="B30" t="n">
-        <v>79227</v>
+        <v>98105</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3553,41 +3553,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493817</v>
+        <v>493917</v>
       </c>
       <c r="R30" t="n">
-        <v>6834627</v>
+        <v>6834563</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3614,19 +3614,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3641,22 +3631,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121463160</v>
+        <v>121461113</v>
       </c>
       <c r="B31" t="n">
-        <v>78610</v>
+        <v>78346</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3669,37 +3659,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>230405</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Barkheden, Barkheden, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494004</v>
+        <v>493790</v>
       </c>
       <c r="R31" t="n">
-        <v>6834553</v>
+        <v>6834696</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3731,7 +3718,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3741,7 +3728,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3750,7 +3737,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3769,10 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121462254</v>
+        <v>121464008</v>
       </c>
       <c r="B32" t="n">
-        <v>98105</v>
+        <v>78346</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3781,41 +3767,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493917</v>
+        <v>494068</v>
       </c>
       <c r="R32" t="n">
-        <v>6834563</v>
+        <v>6834592</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3842,9 +3828,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3859,22 +3855,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121460832</v>
+        <v>121462937</v>
       </c>
       <c r="B33" t="n">
-        <v>79227</v>
+        <v>74715</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3887,34 +3883,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493790</v>
+        <v>494004</v>
       </c>
       <c r="R33" t="n">
-        <v>6834696</v>
+        <v>6834553</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3946,7 +3942,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3956,7 +3952,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3983,7 +3979,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121461098</v>
+        <v>121462206</v>
       </c>
       <c r="B34" t="n">
         <v>78609</v>
@@ -4023,13 +4019,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493790</v>
+        <v>493812</v>
       </c>
       <c r="R34" t="n">
-        <v>6834696</v>
+        <v>6834571</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4058,7 +4054,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4068,7 +4064,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4083,22 +4079,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121462206</v>
+        <v>121463076</v>
       </c>
       <c r="B35" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4111,37 +4107,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493812</v>
+        <v>494009</v>
       </c>
       <c r="R35" t="n">
-        <v>6834571</v>
+        <v>6834588</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4170,7 +4166,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4180,7 +4176,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4207,7 +4203,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121461485</v>
+        <v>121461165</v>
       </c>
       <c r="B36" t="n">
         <v>79227</v>
@@ -4247,10 +4243,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493825</v>
+        <v>493817</v>
       </c>
       <c r="R36" t="n">
-        <v>6834542</v>
+        <v>6834627</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4282,7 +4278,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4292,7 +4288,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4319,10 +4315,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121464008</v>
+        <v>121460788</v>
       </c>
       <c r="B37" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4335,37 +4331,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494068</v>
+        <v>493790</v>
       </c>
       <c r="R37" t="n">
-        <v>6834592</v>
+        <v>6834696</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4394,7 +4390,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4404,7 +4400,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4419,22 +4415,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121463076</v>
+        <v>121460831</v>
       </c>
       <c r="B38" t="n">
-        <v>74715</v>
+        <v>78345</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4447,37 +4443,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494009</v>
+        <v>493790</v>
       </c>
       <c r="R38" t="n">
-        <v>6834588</v>
+        <v>6834696</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4506,7 +4502,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4516,7 +4512,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4531,22 +4527,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121460831</v>
+        <v>121461098</v>
       </c>
       <c r="B39" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4559,27 +4555,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
@@ -4618,7 +4614,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4628,7 +4624,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4648,17 +4644,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121462937</v>
+        <v>121463373</v>
       </c>
       <c r="B40" t="n">
-        <v>74715</v>
+        <v>90685</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4667,41 +4663,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494004</v>
+        <v>494068</v>
       </c>
       <c r="R40" t="n">
-        <v>6834553</v>
+        <v>6834592</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4730,7 +4726,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4740,7 +4736,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4755,22 +4751,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121461113</v>
+        <v>121461485</v>
       </c>
       <c r="B41" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4783,21 +4779,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4807,10 +4803,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493790</v>
+        <v>493825</v>
       </c>
       <c r="R41" t="n">
-        <v>6834696</v>
+        <v>6834542</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4842,7 +4838,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4852,7 +4848,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4872,17 +4868,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121463373</v>
+        <v>121463160</v>
       </c>
       <c r="B42" t="n">
-        <v>90685</v>
+        <v>78610</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4891,41 +4887,44 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>230405</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Barkheden, Barkheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494068</v>
+        <v>494004</v>
       </c>
       <c r="R42" t="n">
-        <v>6834592</v>
+        <v>6834553</v>
       </c>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4954,7 +4953,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4964,7 +4963,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4973,18 +4972,19 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121462243</v>
+        <v>121462834</v>
       </c>
       <c r="B46" t="n">
         <v>78609</v>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493905</v>
+        <v>494009</v>
       </c>
       <c r="R46" t="n">
-        <v>6834568</v>
+        <v>6834570</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5451,7 +5451,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5478,7 +5483,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121463429</v>
+        <v>121463770</v>
       </c>
       <c r="B47" t="n">
         <v>78609</v>
@@ -5518,10 +5523,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494075</v>
+        <v>494125</v>
       </c>
       <c r="R47" t="n">
-        <v>6834606</v>
+        <v>6834588</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5553,7 +5558,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5563,12 +5568,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Tallstam</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5595,7 +5600,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121461118</v>
+        <v>121461121</v>
       </c>
       <c r="B48" t="n">
         <v>98105</v>
@@ -5628,26 +5633,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493869</v>
+        <v>493873</v>
       </c>
       <c r="R48" t="n">
-        <v>6834529</v>
+        <v>6834530</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5679,7 +5675,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5689,7 +5685,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5716,10 +5712,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121463770</v>
+        <v>121461118</v>
       </c>
       <c r="B49" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5728,38 +5724,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494125</v>
+        <v>493869</v>
       </c>
       <c r="R49" t="n">
-        <v>6834588</v>
+        <v>6834529</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -5791,7 +5796,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5801,12 +5806,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Tallstam</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5833,10 +5833,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121462834</v>
+        <v>121462959</v>
       </c>
       <c r="B50" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5845,38 +5845,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494009</v>
+        <v>494001</v>
       </c>
       <c r="R50" t="n">
-        <v>6834570</v>
+        <v>6834589</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -5908,7 +5917,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5918,12 +5927,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5950,7 +5954,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121461167</v>
+        <v>121462243</v>
       </c>
       <c r="B51" t="n">
         <v>78609</v>
@@ -5990,10 +5994,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493883</v>
+        <v>493905</v>
       </c>
       <c r="R51" t="n">
-        <v>6834518</v>
+        <v>6834568</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6025,7 +6029,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6035,12 +6039,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På Tallstamnen</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6067,7 +6066,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121463067</v>
+        <v>121463429</v>
       </c>
       <c r="B52" t="n">
         <v>78609</v>
@@ -6107,10 +6106,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493995</v>
+        <v>494075</v>
       </c>
       <c r="R52" t="n">
-        <v>6834619</v>
+        <v>6834606</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6142,7 +6141,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6152,12 +6151,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Gran och tall</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6184,10 +6183,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121462959</v>
+        <v>121462195</v>
       </c>
       <c r="B53" t="n">
-        <v>98105</v>
+        <v>57509</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6196,47 +6195,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494001</v>
+        <v>493861</v>
       </c>
       <c r="R53" t="n">
-        <v>6834589</v>
+        <v>6834554</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6268,7 +6258,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6278,7 +6268,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6305,10 +6295,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121461121</v>
+        <v>121461167</v>
       </c>
       <c r="B54" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6317,38 +6307,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493873</v>
+        <v>493883</v>
       </c>
       <c r="R54" t="n">
-        <v>6834530</v>
+        <v>6834518</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6391,6 +6381,11 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På Tallstamnen</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6417,10 +6412,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121462195</v>
+        <v>121463067</v>
       </c>
       <c r="B55" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6433,34 +6428,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493861</v>
+        <v>493995</v>
       </c>
       <c r="R55" t="n">
-        <v>6834554</v>
+        <v>6834619</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6492,7 +6487,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6502,7 +6497,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Gran och tall</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121313925</v>
+        <v>121314211</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493790</v>
+        <v>493820</v>
       </c>
       <c r="R2" t="n">
-        <v>6834794</v>
+        <v>6834777</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121316066</v>
+        <v>121314344</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493896</v>
+        <v>493875</v>
       </c>
       <c r="R3" t="n">
-        <v>6834749</v>
+        <v>6834814</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121314297</v>
+        <v>121314027</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493861</v>
+        <v>493811</v>
       </c>
       <c r="R5" t="n">
-        <v>6834789</v>
+        <v>6834771</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121314027</v>
+        <v>121316548</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493811</v>
+        <v>493794</v>
       </c>
       <c r="R6" t="n">
-        <v>6834771</v>
+        <v>6834804</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121316463</v>
+        <v>121313741</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>57509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493838</v>
+        <v>493766</v>
       </c>
       <c r="R7" t="n">
-        <v>6834855</v>
+        <v>6834823</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,22 +1280,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121316548</v>
+        <v>121313238</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493794</v>
+        <v>493815</v>
       </c>
       <c r="R8" t="n">
-        <v>6834804</v>
+        <v>6834929</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121314269</v>
+        <v>121314203</v>
       </c>
       <c r="B9" t="n">
         <v>98105</v>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493864</v>
+        <v>493870</v>
       </c>
       <c r="R9" t="n">
-        <v>6834781</v>
+        <v>6834767</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121314407</v>
+        <v>121316014</v>
       </c>
       <c r="B10" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493810</v>
+        <v>493896</v>
       </c>
       <c r="R10" t="n">
-        <v>6834885</v>
+        <v>6834747</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121315050</v>
+        <v>121313317</v>
       </c>
       <c r="B11" t="n">
-        <v>98105</v>
+        <v>79719</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493937</v>
+        <v>493813</v>
       </c>
       <c r="R11" t="n">
-        <v>6834639</v>
+        <v>6834953</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1683,22 +1688,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121313238</v>
+        <v>121316610</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493815</v>
+        <v>493818</v>
       </c>
       <c r="R12" t="n">
-        <v>6834929</v>
+        <v>6834795</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121316297</v>
+        <v>121315885</v>
       </c>
       <c r="B13" t="n">
         <v>98105</v>
@@ -1837,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493886</v>
+        <v>493917</v>
       </c>
       <c r="R13" t="n">
-        <v>6834817</v>
+        <v>6834746</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1899,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121313133</v>
+        <v>121314365</v>
       </c>
       <c r="B14" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493849</v>
+        <v>493868</v>
       </c>
       <c r="R14" t="n">
-        <v>6834871</v>
+        <v>6834817</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1975,11 +1980,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121314203</v>
+        <v>121314269</v>
       </c>
       <c r="B15" t="n">
         <v>98105</v>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493870</v>
+        <v>493864</v>
       </c>
       <c r="R15" t="n">
-        <v>6834767</v>
+        <v>6834781</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121313317</v>
+        <v>121316126</v>
       </c>
       <c r="B16" t="n">
-        <v>79719</v>
+        <v>98105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493813</v>
+        <v>493898</v>
       </c>
       <c r="R16" t="n">
-        <v>6834953</v>
+        <v>6834798</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2198,19 +2198,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121316014</v>
+        <v>121316463</v>
       </c>
       <c r="B17" t="n">
         <v>98105</v>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493896</v>
+        <v>493838</v>
       </c>
       <c r="R17" t="n">
-        <v>6834747</v>
+        <v>6834855</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121314365</v>
+        <v>121314284</v>
       </c>
       <c r="B18" t="n">
         <v>98105</v>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493868</v>
+        <v>493876</v>
       </c>
       <c r="R18" t="n">
-        <v>6834817</v>
+        <v>6834703</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2402,19 +2402,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121316610</v>
+        <v>121313925</v>
       </c>
       <c r="B19" t="n">
         <v>98105</v>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493818</v>
+        <v>493790</v>
       </c>
       <c r="R19" t="n">
-        <v>6834795</v>
+        <v>6834794</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2504,19 +2504,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121314344</v>
+        <v>121314199</v>
       </c>
       <c r="B20" t="n">
         <v>98105</v>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493875</v>
+        <v>493816</v>
       </c>
       <c r="R20" t="n">
-        <v>6834814</v>
+        <v>6834773</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2606,22 +2606,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121316126</v>
+        <v>121313133</v>
       </c>
       <c r="B21" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493898</v>
+        <v>493849</v>
       </c>
       <c r="R21" t="n">
-        <v>6834798</v>
+        <v>6834871</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2694,6 +2694,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121314199</v>
+        <v>121314407</v>
       </c>
       <c r="B22" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2737,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493816</v>
+        <v>493810</v>
       </c>
       <c r="R22" t="n">
-        <v>6834773</v>
+        <v>6834885</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2810,19 +2815,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121316679</v>
+        <v>121316066</v>
       </c>
       <c r="B23" t="n">
         <v>98105</v>
@@ -2862,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493815</v>
+        <v>493896</v>
       </c>
       <c r="R23" t="n">
-        <v>6834794</v>
+        <v>6834749</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2924,7 +2929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121314284</v>
+        <v>121316679</v>
       </c>
       <c r="B24" t="n">
         <v>98105</v>
@@ -2964,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493876</v>
+        <v>493815</v>
       </c>
       <c r="R24" t="n">
-        <v>6834703</v>
+        <v>6834794</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3014,22 +3019,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121314211</v>
+        <v>121315452</v>
       </c>
       <c r="B25" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3043,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,13 +3071,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493820</v>
+        <v>494000</v>
       </c>
       <c r="R25" t="n">
-        <v>6834777</v>
+        <v>6834510</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3116,22 +3121,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121315452</v>
+        <v>121313915</v>
       </c>
       <c r="B26" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,25 +3145,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,13 +3173,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494000</v>
+        <v>493790</v>
       </c>
       <c r="R26" t="n">
-        <v>6834510</v>
+        <v>6834789</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3230,7 +3235,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121315885</v>
+        <v>121314297</v>
       </c>
       <c r="B27" t="n">
         <v>98105</v>
@@ -3270,13 +3275,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493917</v>
+        <v>493861</v>
       </c>
       <c r="R27" t="n">
-        <v>6834746</v>
+        <v>6834789</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3332,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121313741</v>
+        <v>121315050</v>
       </c>
       <c r="B28" t="n">
-        <v>57509</v>
+        <v>98105</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,25 +3349,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,13 +3377,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493766</v>
+        <v>493937</v>
       </c>
       <c r="R28" t="n">
-        <v>6834823</v>
+        <v>6834639</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3408,11 +3413,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3427,19 +3427,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121313915</v>
+        <v>121316297</v>
       </c>
       <c r="B29" t="n">
         <v>98105</v>
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493790</v>
+        <v>493886</v>
       </c>
       <c r="R29" t="n">
-        <v>6834789</v>
+        <v>6834817</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121462254</v>
+        <v>121463076</v>
       </c>
       <c r="B30" t="n">
-        <v>98105</v>
+        <v>74715</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3553,41 +3553,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493917</v>
+        <v>494009</v>
       </c>
       <c r="R30" t="n">
-        <v>6834563</v>
+        <v>6834588</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3614,9 +3614,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3631,22 +3641,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121461113</v>
+        <v>121462206</v>
       </c>
       <c r="B31" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,21 +3669,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,13 +3693,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493790</v>
+        <v>493812</v>
       </c>
       <c r="R31" t="n">
-        <v>6834696</v>
+        <v>6834571</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3718,7 +3728,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3728,7 +3738,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3743,22 +3753,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121464008</v>
+        <v>121460788</v>
       </c>
       <c r="B32" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3771,37 +3781,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494068</v>
+        <v>493790</v>
       </c>
       <c r="R32" t="n">
-        <v>6834592</v>
+        <v>6834696</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3830,7 +3840,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3840,7 +3850,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3855,22 +3865,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121462937</v>
+        <v>121463160</v>
       </c>
       <c r="B33" t="n">
-        <v>74715</v>
+        <v>78610</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3883,27 +3893,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>230405</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Barkheden, Barkheden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -3942,7 +3955,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3952,7 +3965,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3961,6 +3974,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3979,10 +3993,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121462206</v>
+        <v>121462254</v>
       </c>
       <c r="B34" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3991,41 +4005,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493812</v>
+        <v>493917</v>
       </c>
       <c r="R34" t="n">
-        <v>6834571</v>
+        <v>6834563</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4052,19 +4066,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4079,22 +4083,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121463076</v>
+        <v>121464008</v>
       </c>
       <c r="B35" t="n">
-        <v>74715</v>
+        <v>78346</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4107,21 +4111,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4131,13 +4135,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494009</v>
+        <v>494068</v>
       </c>
       <c r="R35" t="n">
-        <v>6834588</v>
+        <v>6834592</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4166,7 +4170,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4176,7 +4180,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4203,10 +4207,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121461165</v>
+        <v>121461113</v>
       </c>
       <c r="B36" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4219,21 +4223,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4243,10 +4247,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493817</v>
+        <v>493790</v>
       </c>
       <c r="R36" t="n">
-        <v>6834627</v>
+        <v>6834696</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4278,7 +4282,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4288,7 +4292,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4308,14 +4312,14 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121460788</v>
+        <v>121461117</v>
       </c>
       <c r="B37" t="n">
         <v>79227</v>
@@ -4355,10 +4359,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493790</v>
+        <v>493817</v>
       </c>
       <c r="R37" t="n">
-        <v>6834696</v>
+        <v>6834627</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4390,7 +4394,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4400,7 +4404,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4420,7 +4424,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4651,10 +4655,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121463373</v>
+        <v>121462937</v>
       </c>
       <c r="B40" t="n">
-        <v>90685</v>
+        <v>74715</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4663,41 +4667,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494068</v>
+        <v>494004</v>
       </c>
       <c r="R40" t="n">
-        <v>6834592</v>
+        <v>6834553</v>
       </c>
       <c r="S40" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4726,7 +4730,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4736,7 +4740,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4751,12 +4755,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4875,10 +4879,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121463160</v>
+        <v>121463373</v>
       </c>
       <c r="B42" t="n">
-        <v>78610</v>
+        <v>90685</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4887,44 +4891,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>230405</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Barkheden, Barkheden, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494004</v>
+        <v>494068</v>
       </c>
       <c r="R42" t="n">
-        <v>6834553</v>
+        <v>6834592</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4953,7 +4954,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4963,7 +4964,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4972,26 +4973,25 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121463743</v>
+        <v>121463365</v>
       </c>
       <c r="B43" t="n">
         <v>98105</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494116</v>
+        <v>494086</v>
       </c>
       <c r="R43" t="n">
-        <v>6834573</v>
+        <v>6834603</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5241,7 +5241,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121463365</v>
+        <v>121463743</v>
       </c>
       <c r="B45" t="n">
         <v>98105</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494086</v>
+        <v>494116</v>
       </c>
       <c r="R45" t="n">
-        <v>6834603</v>
+        <v>6834573</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5366,7 +5366,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121462834</v>
+        <v>121463770</v>
       </c>
       <c r="B46" t="n">
         <v>78609</v>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494009</v>
+        <v>494125</v>
       </c>
       <c r="R46" t="n">
-        <v>6834570</v>
+        <v>6834588</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Tallstam</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5483,7 +5483,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121463770</v>
+        <v>121461167</v>
       </c>
       <c r="B47" t="n">
         <v>78609</v>
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494125</v>
+        <v>493883</v>
       </c>
       <c r="R47" t="n">
-        <v>6834588</v>
+        <v>6834518</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Tallstam</t>
+          <t>På Tallstamnen</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5600,10 +5600,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121461121</v>
+        <v>121462834</v>
       </c>
       <c r="B48" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5612,38 +5612,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493873</v>
+        <v>494009</v>
       </c>
       <c r="R48" t="n">
-        <v>6834530</v>
+        <v>6834570</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5685,7 +5685,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5712,10 +5717,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121461118</v>
+        <v>121462195</v>
       </c>
       <c r="B49" t="n">
-        <v>98105</v>
+        <v>57509</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5724,47 +5729,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493869</v>
+        <v>493861</v>
       </c>
       <c r="R49" t="n">
-        <v>6834529</v>
+        <v>6834554</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -5796,7 +5792,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5806,7 +5802,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5833,7 +5829,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121462959</v>
+        <v>121461118</v>
       </c>
       <c r="B50" t="n">
         <v>98105</v>
@@ -5868,7 +5864,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5878,14 +5874,14 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494001</v>
+        <v>493869</v>
       </c>
       <c r="R50" t="n">
-        <v>6834589</v>
+        <v>6834529</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -5917,7 +5913,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5927,7 +5923,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5954,10 +5950,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121462243</v>
+        <v>121461121</v>
       </c>
       <c r="B51" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5966,38 +5962,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493905</v>
+        <v>493873</v>
       </c>
       <c r="R51" t="n">
-        <v>6834568</v>
+        <v>6834530</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6029,7 +6025,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6039,7 +6035,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6183,10 +6179,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121462195</v>
+        <v>121462243</v>
       </c>
       <c r="B53" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6199,34 +6195,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493861</v>
+        <v>493905</v>
       </c>
       <c r="R53" t="n">
-        <v>6834554</v>
+        <v>6834568</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6258,7 +6254,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6268,7 +6264,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6295,7 +6291,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121461167</v>
+        <v>121463067</v>
       </c>
       <c r="B54" t="n">
         <v>78609</v>
@@ -6335,10 +6331,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493883</v>
+        <v>493995</v>
       </c>
       <c r="R54" t="n">
-        <v>6834518</v>
+        <v>6834619</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6370,7 +6366,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6380,12 +6376,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På Tallstamnen</t>
+          <t>Gran och tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6412,10 +6408,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121463067</v>
+        <v>121462959</v>
       </c>
       <c r="B55" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6424,38 +6420,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493995</v>
+        <v>494001</v>
       </c>
       <c r="R55" t="n">
-        <v>6834619</v>
+        <v>6834589</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6487,7 +6492,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6497,12 +6502,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Gran och tall</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -3765,10 +3765,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121460788</v>
+        <v>121462254</v>
       </c>
       <c r="B32" t="n">
-        <v>79227</v>
+        <v>98105</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3777,41 +3777,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493790</v>
+        <v>493917</v>
       </c>
       <c r="R32" t="n">
-        <v>6834696</v>
+        <v>6834563</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3838,19 +3838,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>09:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,12 +3855,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3993,10 +3983,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121462254</v>
+        <v>121460788</v>
       </c>
       <c r="B34" t="n">
-        <v>98105</v>
+        <v>79227</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4005,41 +3995,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493917</v>
+        <v>493790</v>
       </c>
       <c r="R34" t="n">
-        <v>6834563</v>
+        <v>6834696</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4066,9 +4056,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4083,12 +4083,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121314211</v>
+        <v>121314344</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493820</v>
+        <v>493875</v>
       </c>
       <c r="R2" t="n">
-        <v>6834777</v>
+        <v>6834814</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121314344</v>
+        <v>121315885</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493875</v>
+        <v>493917</v>
       </c>
       <c r="R3" t="n">
-        <v>6834814</v>
+        <v>6834746</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -882,7 +882,7 @@
         <v>121314972</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121314027</v>
+        <v>121314407</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>79697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493811</v>
+        <v>493810</v>
       </c>
       <c r="R5" t="n">
-        <v>6834771</v>
+        <v>6834885</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121316548</v>
+        <v>121313238</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493794</v>
+        <v>493815</v>
       </c>
       <c r="R6" t="n">
-        <v>6834804</v>
+        <v>6834929</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121313741</v>
+        <v>121316610</v>
       </c>
       <c r="B7" t="n">
-        <v>57509</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493766</v>
+        <v>493818</v>
       </c>
       <c r="R7" t="n">
-        <v>6834823</v>
+        <v>6834795</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,11 +1261,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121313238</v>
+        <v>121313317</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>79726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493815</v>
+        <v>493813</v>
       </c>
       <c r="R8" t="n">
-        <v>6834929</v>
+        <v>6834953</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121314203</v>
+        <v>121314027</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493870</v>
+        <v>493811</v>
       </c>
       <c r="R9" t="n">
-        <v>6834767</v>
+        <v>6834771</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1484,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121316014</v>
+        <v>121314297</v>
       </c>
       <c r="B10" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493896</v>
+        <v>493861</v>
       </c>
       <c r="R10" t="n">
-        <v>6834747</v>
+        <v>6834789</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121313317</v>
+        <v>121316679</v>
       </c>
       <c r="B11" t="n">
-        <v>79719</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493813</v>
+        <v>493815</v>
       </c>
       <c r="R11" t="n">
-        <v>6834953</v>
+        <v>6834794</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1688,22 +1683,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121316610</v>
+        <v>121316126</v>
       </c>
       <c r="B12" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493818</v>
+        <v>493898</v>
       </c>
       <c r="R12" t="n">
-        <v>6834795</v>
+        <v>6834798</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121315885</v>
+        <v>121313741</v>
       </c>
       <c r="B13" t="n">
-        <v>98105</v>
+        <v>57510</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493917</v>
+        <v>493766</v>
       </c>
       <c r="R13" t="n">
-        <v>6834746</v>
+        <v>6834823</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1878,6 +1873,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1892,22 +1892,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121314365</v>
+        <v>121315452</v>
       </c>
       <c r="B14" t="n">
-        <v>98105</v>
+        <v>79697</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493868</v>
+        <v>494000</v>
       </c>
       <c r="R14" t="n">
-        <v>6834817</v>
+        <v>6834510</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121314269</v>
+        <v>121313133</v>
       </c>
       <c r="B15" t="n">
-        <v>98105</v>
+        <v>79697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493864</v>
+        <v>493849</v>
       </c>
       <c r="R15" t="n">
-        <v>6834781</v>
+        <v>6834871</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2082,6 +2082,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121316126</v>
+        <v>121314269</v>
       </c>
       <c r="B16" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493898</v>
+        <v>493864</v>
       </c>
       <c r="R16" t="n">
-        <v>6834798</v>
+        <v>6834781</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121316463</v>
+        <v>121314203</v>
       </c>
       <c r="B17" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493838</v>
+        <v>493870</v>
       </c>
       <c r="R17" t="n">
-        <v>6834855</v>
+        <v>6834767</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121314284</v>
+        <v>121314211</v>
       </c>
       <c r="B18" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,13 +2357,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493876</v>
+        <v>493820</v>
       </c>
       <c r="R18" t="n">
-        <v>6834703</v>
+        <v>6834777</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121313925</v>
+        <v>121316014</v>
       </c>
       <c r="B19" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493790</v>
+        <v>493896</v>
       </c>
       <c r="R19" t="n">
-        <v>6834794</v>
+        <v>6834747</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2504,22 +2509,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121314199</v>
+        <v>121314284</v>
       </c>
       <c r="B20" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493816</v>
+        <v>493876</v>
       </c>
       <c r="R20" t="n">
-        <v>6834773</v>
+        <v>6834703</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2618,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121313133</v>
+        <v>121316066</v>
       </c>
       <c r="B21" t="n">
-        <v>79690</v>
+        <v>98113</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2635,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493849</v>
+        <v>493896</v>
       </c>
       <c r="R21" t="n">
-        <v>6834871</v>
+        <v>6834749</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2694,11 +2699,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2725,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121314407</v>
+        <v>121314199</v>
       </c>
       <c r="B22" t="n">
-        <v>79690</v>
+        <v>98113</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2737,25 +2737,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493810</v>
+        <v>493816</v>
       </c>
       <c r="R22" t="n">
-        <v>6834885</v>
+        <v>6834773</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2815,22 +2815,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121316066</v>
+        <v>121315050</v>
       </c>
       <c r="B23" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493896</v>
+        <v>493937</v>
       </c>
       <c r="R23" t="n">
-        <v>6834749</v>
+        <v>6834639</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121316679</v>
+        <v>121316297</v>
       </c>
       <c r="B24" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2969,13 +2969,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493815</v>
+        <v>493886</v>
       </c>
       <c r="R24" t="n">
-        <v>6834794</v>
+        <v>6834817</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121315452</v>
+        <v>121313915</v>
       </c>
       <c r="B25" t="n">
-        <v>79690</v>
+        <v>98113</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3043,25 +3043,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,13 +3071,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494000</v>
+        <v>493790</v>
       </c>
       <c r="R25" t="n">
-        <v>6834510</v>
+        <v>6834789</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121313915</v>
+        <v>121314365</v>
       </c>
       <c r="B26" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493790</v>
+        <v>493868</v>
       </c>
       <c r="R26" t="n">
-        <v>6834789</v>
+        <v>6834817</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121314297</v>
+        <v>121316463</v>
       </c>
       <c r="B27" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493861</v>
+        <v>493838</v>
       </c>
       <c r="R27" t="n">
-        <v>6834789</v>
+        <v>6834855</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121315050</v>
+        <v>121313925</v>
       </c>
       <c r="B28" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493937</v>
+        <v>493790</v>
       </c>
       <c r="R28" t="n">
-        <v>6834639</v>
+        <v>6834794</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3427,22 +3427,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121316297</v>
+        <v>121316548</v>
       </c>
       <c r="B29" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493886</v>
+        <v>493794</v>
       </c>
       <c r="R29" t="n">
-        <v>6834817</v>
+        <v>6834804</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121463076</v>
+        <v>121461117</v>
       </c>
       <c r="B30" t="n">
-        <v>74715</v>
+        <v>79234</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,37 +3557,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494009</v>
+        <v>493817</v>
       </c>
       <c r="R30" t="n">
-        <v>6834588</v>
+        <v>6834627</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3641,22 +3641,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121462206</v>
+        <v>121463373</v>
       </c>
       <c r="B31" t="n">
-        <v>78609</v>
+        <v>90693</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3665,41 +3665,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493812</v>
+        <v>494068</v>
       </c>
       <c r="R31" t="n">
-        <v>6834571</v>
+        <v>6834592</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3765,10 +3765,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121462254</v>
+        <v>121462206</v>
       </c>
       <c r="B32" t="n">
-        <v>98105</v>
+        <v>78616</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3777,41 +3777,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493917</v>
+        <v>493812</v>
       </c>
       <c r="R32" t="n">
-        <v>6834563</v>
+        <v>6834571</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3838,9 +3838,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3855,22 +3865,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121463160</v>
+        <v>121461485</v>
       </c>
       <c r="B33" t="n">
-        <v>78610</v>
+        <v>79234</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3883,37 +3893,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>230405</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Barkheden, Barkheden, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494004</v>
+        <v>493825</v>
       </c>
       <c r="R33" t="n">
-        <v>6834553</v>
+        <v>6834542</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3945,7 +3952,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3955,7 +3962,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3964,7 +3971,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3976,7 +3982,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3986,7 +3992,7 @@
         <v>121460788</v>
       </c>
       <c r="B34" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4095,10 +4101,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121464008</v>
+        <v>121460831</v>
       </c>
       <c r="B35" t="n">
-        <v>78346</v>
+        <v>78352</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4111,37 +4117,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494068</v>
+        <v>493790</v>
       </c>
       <c r="R35" t="n">
-        <v>6834592</v>
+        <v>6834696</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4170,7 +4176,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4180,7 +4186,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4195,22 +4201,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121461113</v>
+        <v>121462254</v>
       </c>
       <c r="B36" t="n">
-        <v>78346</v>
+        <v>98113</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4219,41 +4225,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493790</v>
+        <v>493917</v>
       </c>
       <c r="R36" t="n">
-        <v>6834696</v>
+        <v>6834563</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4280,19 +4286,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:56</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4307,22 +4303,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121461117</v>
+        <v>121461113</v>
       </c>
       <c r="B37" t="n">
-        <v>79227</v>
+        <v>78353</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4335,21 +4331,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4359,10 +4355,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493817</v>
+        <v>493790</v>
       </c>
       <c r="R37" t="n">
-        <v>6834627</v>
+        <v>6834696</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4394,7 +4390,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4404,7 +4400,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4424,17 +4420,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121460831</v>
+        <v>121464008</v>
       </c>
       <c r="B38" t="n">
-        <v>78345</v>
+        <v>78353</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4447,37 +4443,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493790</v>
+        <v>494068</v>
       </c>
       <c r="R38" t="n">
-        <v>6834696</v>
+        <v>6834592</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4506,7 +4502,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4516,7 +4512,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4531,12 +4527,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4546,7 +4542,7 @@
         <v>121461098</v>
       </c>
       <c r="B39" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4655,10 +4651,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121462937</v>
+        <v>121463076</v>
       </c>
       <c r="B40" t="n">
-        <v>74715</v>
+        <v>74722</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4691,17 +4687,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494004</v>
+        <v>494009</v>
       </c>
       <c r="R40" t="n">
-        <v>6834553</v>
+        <v>6834588</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4730,7 +4726,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4740,7 +4736,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4755,22 +4751,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121461485</v>
+        <v>121462937</v>
       </c>
       <c r="B41" t="n">
-        <v>79227</v>
+        <v>74722</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4783,21 +4779,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4807,10 +4803,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493825</v>
+        <v>494004</v>
       </c>
       <c r="R41" t="n">
-        <v>6834542</v>
+        <v>6834553</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4842,7 +4838,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4852,7 +4848,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4872,17 +4868,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121463373</v>
+        <v>121463160</v>
       </c>
       <c r="B42" t="n">
-        <v>90685</v>
+        <v>78617</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4891,41 +4887,44 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>230405</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Barkheden, Barkheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494068</v>
+        <v>494004</v>
       </c>
       <c r="R42" t="n">
-        <v>6834592</v>
+        <v>6834553</v>
       </c>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4954,7 +4953,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4964,7 +4963,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4973,28 +4972,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121463365</v>
+        <v>121463131</v>
       </c>
       <c r="B43" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494086</v>
+        <v>494081</v>
       </c>
       <c r="R43" t="n">
-        <v>6834603</v>
+        <v>6834614</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5116,10 +5116,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121463131</v>
+        <v>121463365</v>
       </c>
       <c r="B44" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5168,10 +5168,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494081</v>
+        <v>494086</v>
       </c>
       <c r="R44" t="n">
-        <v>6834614</v>
+        <v>6834603</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,7 +5244,7 @@
         <v>121463743</v>
       </c>
       <c r="B45" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5366,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121463770</v>
+        <v>121463429</v>
       </c>
       <c r="B46" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494125</v>
+        <v>494075</v>
       </c>
       <c r="R46" t="n">
-        <v>6834588</v>
+        <v>6834606</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Tallstam</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5483,10 +5483,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121461167</v>
+        <v>121463067</v>
       </c>
       <c r="B47" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493883</v>
+        <v>493995</v>
       </c>
       <c r="R47" t="n">
-        <v>6834518</v>
+        <v>6834619</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På Tallstamnen</t>
+          <t>Gran och tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5600,10 +5600,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121462834</v>
+        <v>121462195</v>
       </c>
       <c r="B48" t="n">
-        <v>78609</v>
+        <v>57510</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5616,34 +5616,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494009</v>
+        <v>493861</v>
       </c>
       <c r="R48" t="n">
-        <v>6834570</v>
+        <v>6834554</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5685,12 +5685,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5717,10 +5712,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121462195</v>
+        <v>121461121</v>
       </c>
       <c r="B49" t="n">
-        <v>57509</v>
+        <v>98113</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5729,25 +5724,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5757,10 +5752,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493861</v>
+        <v>493873</v>
       </c>
       <c r="R49" t="n">
-        <v>6834554</v>
+        <v>6834530</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -5792,7 +5787,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5802,7 +5797,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5832,7 +5827,7 @@
         <v>121461118</v>
       </c>
       <c r="B50" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5950,10 +5945,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121461121</v>
+        <v>121462959</v>
       </c>
       <c r="B51" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5983,17 +5978,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493873</v>
+        <v>494001</v>
       </c>
       <c r="R51" t="n">
-        <v>6834530</v>
+        <v>6834589</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6025,7 +6029,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6035,7 +6039,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6062,10 +6066,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121463429</v>
+        <v>121462243</v>
       </c>
       <c r="B52" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6102,10 +6106,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494075</v>
+        <v>493905</v>
       </c>
       <c r="R52" t="n">
-        <v>6834606</v>
+        <v>6834568</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6137,7 +6141,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6147,12 +6151,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6179,10 +6178,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121462243</v>
+        <v>121461167</v>
       </c>
       <c r="B53" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6219,10 +6218,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493905</v>
+        <v>493883</v>
       </c>
       <c r="R53" t="n">
-        <v>6834568</v>
+        <v>6834518</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6254,7 +6253,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6264,7 +6263,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På Tallstamnen</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6291,10 +6295,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121463067</v>
+        <v>121462834</v>
       </c>
       <c r="B54" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6331,10 +6335,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493995</v>
+        <v>494009</v>
       </c>
       <c r="R54" t="n">
-        <v>6834619</v>
+        <v>6834570</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6366,7 +6370,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6376,12 +6380,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Gran och tall</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6408,10 +6412,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121462959</v>
+        <v>121463770</v>
       </c>
       <c r="B55" t="n">
-        <v>98105</v>
+        <v>78616</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6420,47 +6424,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494001</v>
+        <v>494125</v>
       </c>
       <c r="R55" t="n">
-        <v>6834589</v>
+        <v>6834588</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6492,7 +6487,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6502,7 +6497,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Tallstam</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121316610</v>
+        <v>121314027</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493818</v>
+        <v>493811</v>
       </c>
       <c r="R7" t="n">
-        <v>6834795</v>
+        <v>6834771</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1275,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121314027</v>
+        <v>121316610</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493811</v>
+        <v>493818</v>
       </c>
       <c r="R9" t="n">
-        <v>6834771</v>
+        <v>6834795</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1479,12 +1479,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121313741</v>
+        <v>121314269</v>
       </c>
       <c r="B13" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493766</v>
+        <v>493864</v>
       </c>
       <c r="R13" t="n">
-        <v>6834823</v>
+        <v>6834781</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1873,11 +1873,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1892,22 +1887,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121315452</v>
+        <v>121314203</v>
       </c>
       <c r="B14" t="n">
-        <v>79697</v>
+        <v>98113</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494000</v>
+        <v>493870</v>
       </c>
       <c r="R14" t="n">
-        <v>6834510</v>
+        <v>6834767</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121313133</v>
+        <v>121313741</v>
       </c>
       <c r="B15" t="n">
-        <v>79697</v>
+        <v>57510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,13 +2041,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493849</v>
+        <v>493766</v>
       </c>
       <c r="R15" t="n">
-        <v>6834871</v>
+        <v>6834823</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2086,7 +2081,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2101,22 +2096,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121314269</v>
+        <v>121315452</v>
       </c>
       <c r="B16" t="n">
-        <v>98113</v>
+        <v>79697</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493864</v>
+        <v>494000</v>
       </c>
       <c r="R16" t="n">
-        <v>6834781</v>
+        <v>6834510</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2215,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121314203</v>
+        <v>121313133</v>
       </c>
       <c r="B17" t="n">
-        <v>98113</v>
+        <v>79697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493870</v>
+        <v>493849</v>
       </c>
       <c r="R17" t="n">
-        <v>6834767</v>
+        <v>6834871</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2291,6 +2286,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121460831</v>
+        <v>121461165</v>
       </c>
       <c r="B30" t="n">
-        <v>78352</v>
+        <v>79234</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,34 +3557,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493790</v>
+        <v>493817</v>
       </c>
       <c r="R30" t="n">
-        <v>6834696</v>
+        <v>6834627</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3765,10 +3765,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121464008</v>
+        <v>121462206</v>
       </c>
       <c r="B32" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3781,37 +3781,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494068</v>
+        <v>493812</v>
       </c>
       <c r="R32" t="n">
-        <v>6834592</v>
+        <v>6834571</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3877,10 +3877,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121463160</v>
+        <v>121462254</v>
       </c>
       <c r="B33" t="n">
-        <v>78617</v>
+        <v>98113</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3889,44 +3889,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>230405</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Barkheden, Barkheden, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494004</v>
+        <v>493917</v>
       </c>
       <c r="R33" t="n">
-        <v>6834553</v>
+        <v>6834563</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3953,50 +3950,39 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121462937</v>
+        <v>121460831</v>
       </c>
       <c r="B34" t="n">
-        <v>74722</v>
+        <v>78352</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4009,34 +3995,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494004</v>
+        <v>493790</v>
       </c>
       <c r="R34" t="n">
-        <v>6834553</v>
+        <v>6834696</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4068,7 +4054,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4078,7 +4064,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4105,7 +4091,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121462206</v>
+        <v>121461098</v>
       </c>
       <c r="B35" t="n">
         <v>78616</v>
@@ -4145,13 +4131,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493812</v>
+        <v>493790</v>
       </c>
       <c r="R35" t="n">
-        <v>6834571</v>
+        <v>6834696</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4180,7 +4166,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4190,7 +4176,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4205,19 +4191,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121461165</v>
+        <v>121460832</v>
       </c>
       <c r="B36" t="n">
         <v>79234</v>
@@ -4253,14 +4239,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493817</v>
+        <v>493790</v>
       </c>
       <c r="R36" t="n">
-        <v>6834627</v>
+        <v>6834696</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4292,7 +4278,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4302,7 +4288,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4322,17 +4308,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121460788</v>
+        <v>121463076</v>
       </c>
       <c r="B37" t="n">
-        <v>79234</v>
+        <v>74722</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4345,37 +4331,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493790</v>
+        <v>494009</v>
       </c>
       <c r="R37" t="n">
-        <v>6834696</v>
+        <v>6834588</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4404,7 +4390,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4414,7 +4400,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4429,22 +4415,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121461098</v>
+        <v>121464008</v>
       </c>
       <c r="B38" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4457,37 +4443,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493790</v>
+        <v>494068</v>
       </c>
       <c r="R38" t="n">
-        <v>6834696</v>
+        <v>6834592</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4516,7 +4502,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4526,7 +4512,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4541,22 +4527,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121463076</v>
+        <v>121463160</v>
       </c>
       <c r="B39" t="n">
-        <v>74722</v>
+        <v>78617</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4569,37 +4555,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>230405</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Barkheden, Barkheden, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494009</v>
+        <v>494004</v>
       </c>
       <c r="R39" t="n">
-        <v>6834588</v>
+        <v>6834553</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4628,7 +4617,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4638,7 +4627,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4647,28 +4636,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121463373</v>
+        <v>121462937</v>
       </c>
       <c r="B40" t="n">
-        <v>90693</v>
+        <v>74722</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4677,41 +4667,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494068</v>
+        <v>494004</v>
       </c>
       <c r="R40" t="n">
-        <v>6834592</v>
+        <v>6834553</v>
       </c>
       <c r="S40" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4740,7 +4730,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4750,7 +4740,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4765,22 +4755,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121462254</v>
+        <v>121463373</v>
       </c>
       <c r="B41" t="n">
-        <v>98113</v>
+        <v>90693</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4789,41 +4779,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493917</v>
+        <v>494068</v>
       </c>
       <c r="R41" t="n">
-        <v>6834563</v>
+        <v>6834592</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4850,9 +4840,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4867,12 +4867,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4991,7 +4991,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121463365</v>
+        <v>121463131</v>
       </c>
       <c r="B43" t="n">
         <v>98113</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494086</v>
+        <v>494081</v>
       </c>
       <c r="R43" t="n">
-        <v>6834603</v>
+        <v>6834614</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5241,7 +5241,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121463131</v>
+        <v>121463365</v>
       </c>
       <c r="B45" t="n">
         <v>98113</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494081</v>
+        <v>494086</v>
       </c>
       <c r="R45" t="n">
-        <v>6834614</v>
+        <v>6834603</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5366,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121462195</v>
+        <v>121461121</v>
       </c>
       <c r="B46" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5378,25 +5378,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493861</v>
+        <v>493873</v>
       </c>
       <c r="R46" t="n">
-        <v>6834554</v>
+        <v>6834530</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5478,10 +5478,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121461118</v>
+        <v>121463429</v>
       </c>
       <c r="B47" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5490,47 +5490,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493869</v>
+        <v>494075</v>
       </c>
       <c r="R47" t="n">
-        <v>6834529</v>
+        <v>6834606</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5562,7 +5553,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5572,7 +5563,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5599,10 +5595,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121461121</v>
+        <v>121463770</v>
       </c>
       <c r="B48" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5611,38 +5607,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493873</v>
+        <v>494125</v>
       </c>
       <c r="R48" t="n">
-        <v>6834530</v>
+        <v>6834588</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5674,7 +5670,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5684,7 +5680,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Tallstam</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5711,7 +5712,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121463067</v>
+        <v>121462243</v>
       </c>
       <c r="B49" t="n">
         <v>78616</v>
@@ -5751,10 +5752,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493995</v>
+        <v>493905</v>
       </c>
       <c r="R49" t="n">
-        <v>6834619</v>
+        <v>6834568</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -5786,7 +5787,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5796,12 +5797,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Gran och tall</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5828,7 +5824,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121462243</v>
+        <v>121463067</v>
       </c>
       <c r="B50" t="n">
         <v>78616</v>
@@ -5868,10 +5864,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493905</v>
+        <v>493995</v>
       </c>
       <c r="R50" t="n">
-        <v>6834568</v>
+        <v>6834619</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -5903,7 +5899,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5913,7 +5909,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Gran och tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6057,7 +6058,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121463770</v>
+        <v>121461167</v>
       </c>
       <c r="B52" t="n">
         <v>78616</v>
@@ -6097,10 +6098,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494125</v>
+        <v>493883</v>
       </c>
       <c r="R52" t="n">
-        <v>6834588</v>
+        <v>6834518</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6132,7 +6133,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6142,12 +6143,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Tallstam</t>
+          <t>På Tallstamnen</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6174,10 +6175,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121463429</v>
+        <v>121461118</v>
       </c>
       <c r="B53" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6186,38 +6187,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494075</v>
+        <v>493869</v>
       </c>
       <c r="R53" t="n">
-        <v>6834606</v>
+        <v>6834529</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6249,7 +6259,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6259,12 +6269,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6291,10 +6296,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121461167</v>
+        <v>121462195</v>
       </c>
       <c r="B54" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6307,34 +6312,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493883</v>
+        <v>493861</v>
       </c>
       <c r="R54" t="n">
-        <v>6834518</v>
+        <v>6834554</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6366,7 +6371,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6376,12 +6381,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På Tallstamnen</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -4315,10 +4315,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121463076</v>
+        <v>121464008</v>
       </c>
       <c r="B37" t="n">
-        <v>74722</v>
+        <v>78353</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4331,21 +4331,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494009</v>
+        <v>494068</v>
       </c>
       <c r="R37" t="n">
-        <v>6834588</v>
+        <v>6834592</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4427,10 +4427,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121464008</v>
+        <v>121463076</v>
       </c>
       <c r="B38" t="n">
-        <v>78353</v>
+        <v>74722</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4443,21 +4443,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494068</v>
+        <v>494009</v>
       </c>
       <c r="R38" t="n">
-        <v>6834592</v>
+        <v>6834588</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -3541,7 +3541,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121461165</v>
+        <v>121461117</v>
       </c>
       <c r="B30" t="n">
         <v>79234</v>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121461485</v>
+        <v>121463076</v>
       </c>
       <c r="B31" t="n">
-        <v>79234</v>
+        <v>74722</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3669,37 +3669,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493825</v>
+        <v>494009</v>
       </c>
       <c r="R31" t="n">
-        <v>6834542</v>
+        <v>6834588</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3753,22 +3753,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121462206</v>
+        <v>121460788</v>
       </c>
       <c r="B32" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3805,13 +3805,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493812</v>
+        <v>493790</v>
       </c>
       <c r="R32" t="n">
-        <v>6834571</v>
+        <v>6834696</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,22 +3865,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121462254</v>
+        <v>121461113</v>
       </c>
       <c r="B33" t="n">
-        <v>98113</v>
+        <v>78353</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3889,41 +3889,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493917</v>
+        <v>493790</v>
       </c>
       <c r="R33" t="n">
-        <v>6834563</v>
+        <v>6834696</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3950,9 +3950,19 @@
           <t>2024-12-04</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3967,22 +3977,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121460831</v>
+        <v>121462254</v>
       </c>
       <c r="B34" t="n">
-        <v>78352</v>
+        <v>98113</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3991,41 +4001,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493790</v>
+        <v>493917</v>
       </c>
       <c r="R34" t="n">
-        <v>6834696</v>
+        <v>6834563</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4052,19 +4062,9 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>09:31</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>09:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4079,19 +4079,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121461098</v>
+        <v>121462206</v>
       </c>
       <c r="B35" t="n">
         <v>78616</v>
@@ -4131,13 +4131,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493790</v>
+        <v>493812</v>
       </c>
       <c r="R35" t="n">
-        <v>6834696</v>
+        <v>6834571</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4191,22 +4191,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121460832</v>
+        <v>121464008</v>
       </c>
       <c r="B36" t="n">
-        <v>79234</v>
+        <v>78353</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4219,37 +4219,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pipmyran, Pipmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493790</v>
+        <v>494068</v>
       </c>
       <c r="R36" t="n">
-        <v>6834696</v>
+        <v>6834592</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4303,22 +4303,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121464008</v>
+        <v>121462937</v>
       </c>
       <c r="B37" t="n">
-        <v>78353</v>
+        <v>74722</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4331,37 +4331,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494068</v>
+        <v>494004</v>
       </c>
       <c r="R37" t="n">
-        <v>6834592</v>
+        <v>6834553</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4415,22 +4415,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121463076</v>
+        <v>121463373</v>
       </c>
       <c r="B38" t="n">
-        <v>74722</v>
+        <v>90693</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4439,25 +4439,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494009</v>
+        <v>494068</v>
       </c>
       <c r="R38" t="n">
-        <v>6834588</v>
+        <v>6834592</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4655,10 +4655,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121462937</v>
+        <v>121461098</v>
       </c>
       <c r="B40" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4671,21 +4671,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494004</v>
+        <v>493790</v>
       </c>
       <c r="R40" t="n">
-        <v>6834553</v>
+        <v>6834696</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121463373</v>
+        <v>121460831</v>
       </c>
       <c r="B41" t="n">
-        <v>90693</v>
+        <v>78352</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4779,41 +4779,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Pipmyran, Pipmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494068</v>
+        <v>493790</v>
       </c>
       <c r="R41" t="n">
-        <v>6834592</v>
+        <v>6834696</v>
       </c>
       <c r="S41" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4867,22 +4867,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121461113</v>
+        <v>121461485</v>
       </c>
       <c r="B42" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4895,21 +4895,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493790</v>
+        <v>493825</v>
       </c>
       <c r="R42" t="n">
-        <v>6834696</v>
+        <v>6834542</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4984,14 +4984,14 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn, Anders Heggestad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121463131</v>
+        <v>121463365</v>
       </c>
       <c r="B43" t="n">
         <v>98113</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494081</v>
+        <v>494086</v>
       </c>
       <c r="R43" t="n">
-        <v>6834614</v>
+        <v>6834603</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5241,7 +5241,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121463365</v>
+        <v>121463131</v>
       </c>
       <c r="B45" t="n">
         <v>98113</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494086</v>
+        <v>494081</v>
       </c>
       <c r="R45" t="n">
-        <v>6834603</v>
+        <v>6834614</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5366,7 +5366,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121461121</v>
+        <v>121461118</v>
       </c>
       <c r="B46" t="n">
         <v>98113</v>
@@ -5399,17 +5399,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493873</v>
+        <v>493869</v>
       </c>
       <c r="R46" t="n">
-        <v>6834530</v>
+        <v>6834529</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5441,7 +5450,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5451,7 +5460,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5478,7 +5487,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121463429</v>
+        <v>121462243</v>
       </c>
       <c r="B47" t="n">
         <v>78616</v>
@@ -5518,10 +5527,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494075</v>
+        <v>493905</v>
       </c>
       <c r="R47" t="n">
-        <v>6834606</v>
+        <v>6834568</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5553,7 +5562,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5563,12 +5572,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5595,7 +5599,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121463770</v>
+        <v>121461167</v>
       </c>
       <c r="B48" t="n">
         <v>78616</v>
@@ -5635,10 +5639,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494125</v>
+        <v>493883</v>
       </c>
       <c r="R48" t="n">
-        <v>6834588</v>
+        <v>6834518</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -5670,7 +5674,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5680,12 +5684,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Tallstam</t>
+          <t>På Tallstamnen</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5712,10 +5716,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121462243</v>
+        <v>121462959</v>
       </c>
       <c r="B49" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5724,38 +5728,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493905</v>
+        <v>494001</v>
       </c>
       <c r="R49" t="n">
-        <v>6834568</v>
+        <v>6834589</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -5787,7 +5800,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5797,7 +5810,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5824,7 +5837,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121463067</v>
+        <v>121463429</v>
       </c>
       <c r="B50" t="n">
         <v>78616</v>
@@ -5864,10 +5877,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493995</v>
+        <v>494075</v>
       </c>
       <c r="R50" t="n">
-        <v>6834619</v>
+        <v>6834606</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -5899,7 +5912,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5909,12 +5922,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Gran och tall</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6058,10 +6071,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121461167</v>
+        <v>121462195</v>
       </c>
       <c r="B52" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6074,34 +6087,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493883</v>
+        <v>493861</v>
       </c>
       <c r="R52" t="n">
-        <v>6834518</v>
+        <v>6834554</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6133,7 +6146,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6143,12 +6156,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På Tallstamnen</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6175,10 +6183,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121461118</v>
+        <v>121463067</v>
       </c>
       <c r="B53" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6187,47 +6195,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493869</v>
+        <v>493995</v>
       </c>
       <c r="R53" t="n">
-        <v>6834529</v>
+        <v>6834619</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6259,7 +6258,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6269,7 +6268,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Gran och tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6296,10 +6300,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121462195</v>
+        <v>121463770</v>
       </c>
       <c r="B54" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6312,34 +6316,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493861</v>
+        <v>494125</v>
       </c>
       <c r="R54" t="n">
-        <v>6834554</v>
+        <v>6834588</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6371,7 +6375,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6381,7 +6385,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Tallstam</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6408,7 +6417,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121462959</v>
+        <v>121461121</v>
       </c>
       <c r="B55" t="n">
         <v>98113</v>
@@ -6441,26 +6450,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Olsmässmyran, Olsmässmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494001</v>
+        <v>493873</v>
       </c>
       <c r="R55" t="n">
-        <v>6834589</v>
+        <v>6834530</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6527,6 +6527,108 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>121313322</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>493813</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6834953</v>
+      </c>
+      <c r="S56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53006-2024 artfynd.xlsx
+++ b/artfynd/A 53006-2024 artfynd.xlsx
@@ -6532,7 +6532,7 @@
         <v>121313322</v>
       </c>
       <c r="B56" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
